--- a/docs/14_servicer_fcl_field_spec.xlsx
+++ b/docs/14_servicer_fcl_field_spec.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -225,8 +225,14 @@
       <name val="Consolas"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -371,6 +377,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00385723"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
       </patternFill>
     </fill>
   </fills>
@@ -528,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -885,6 +906,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3207,7 +3258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:T103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="5" customWidth="1" style="74" min="1" max="1"/>
@@ -3221,9 +3272,12 @@
     <col width="32.6328125" customWidth="1" style="74" min="9" max="9"/>
     <col width="18" customWidth="1" style="74" min="10" max="10"/>
     <col width="28.7265625" customWidth="1" style="74" min="11" max="12"/>
+    <col width="52" customWidth="1" style="74" min="12" max="12"/>
     <col width="82" customWidth="1" style="74" min="13" max="13"/>
     <col width="62" customWidth="1" style="74" min="14" max="14"/>
     <col width="31.1796875" customWidth="1" style="74" min="15" max="17"/>
+    <col width="72" customWidth="1" style="74" min="18" max="18"/>
+    <col width="72" customWidth="1" style="74" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="74">
@@ -3282,34 +3336,49 @@
           <t>BPS面板/功能</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="129" t="inlineStr">
+        <is>
+          <t>Newrez → BPS 规则（doc 13/16）</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Newrez状态</t>
         </is>
       </c>
-      <c r="M1" s="58" t="inlineStr">
-        <is>
-          <t>验证SQL（取值范围/样例）</t>
-        </is>
-      </c>
-      <c r="N1" s="67" t="inlineStr">
-        <is>
-          <t>验证结果（实测 2026-06-02）</t>
-        </is>
-      </c>
-      <c r="O1" s="63" t="inlineStr">
+      <c r="N1" s="125" t="inlineStr">
+        <is>
+          <t>Newrez验证SQL（取值范围/样例；数据日 2026-06-01）</t>
+        </is>
+      </c>
+      <c r="O1" s="67" t="inlineStr">
+        <is>
+          <t>Newrez验证结果（数据日 2026-06-01｜实测 2026-06-02）</t>
+        </is>
+      </c>
+      <c r="P1" s="63" t="inlineStr">
         <is>
           <t>人工-Newrez验证结果</t>
         </is>
       </c>
-      <c r="P1" s="63" t="inlineStr">
+      <c r="Q1" s="63" t="inlineStr">
         <is>
           <t>人工-BPS表验证</t>
         </is>
       </c>
-      <c r="Q1" s="63" t="inlineStr">
+      <c r="R1" s="63" t="inlineStr">
         <is>
           <t>人工-BPS表验证查询结果</t>
+        </is>
+      </c>
+      <c r="S1" s="123" t="inlineStr">
+        <is>
+          <t>BPS验证SQL（prod 取值；数据日 2026-06-01）</t>
+        </is>
+      </c>
+      <c r="T1" s="123" t="inlineStr">
+        <is>
+          <t>BPS验证结果（数据日 2026-06-01｜实测 2026-06-04）</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3398,7 @@
       <c r="I2" s="70" t="n"/>
       <c r="J2" s="71" t="n"/>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1" s="74">
       <c r="A3" s="11" t="n">
@@ -3404,29 +3473,34 @@
           <t>ETL入库过滤 / FCL状态判断 / BPS所有面板</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="130" t="inlineStr">
+        <is>
+          <t>N/A — 四维状态，不经 BPS FCL 同步表</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供 (12K+ active FCL行)</t>
         </is>
       </c>
-      <c r="M3" s="59" t="inlineStr">
+      <c r="N3" s="126" t="inlineStr">
         <is>
           <t>-- 验证 delinquency_status 取值范围
 -- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, delinquency_status_mba AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezgeneral
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezgeneral)
+WHERE  dataasof = '2026-06-01'
   AND  delinquency_status_mba IS NOT NULL AND delinquency_status_mba != ''
 GROUP  BY dataasof, delinquency_status_mba ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N3" s="68" t="inlineStr">
+      <c r="O3" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 1-29 DPD:2161 | Current:2053 | Full Payoff:678 | 30-59 DPD:64 | Foreclosure:30 | 60-89 DPD:18 | 90-119 DPD:10 | 120-149 DPD:8 | REO:5 | Service Release:4 | Performing Bankruptcy:4 | Foreclosure / Non-Perf BK:3 | 3rd Party Sale:3 | Non-Performing Bankruptcy:3 | Foreclosure / Perf BK:3 | 180+ DPD:2 | Settlement:1 | REO Sale:1 | 150-179 DPD:1</t>
         </is>
       </c>
-      <c r="O3" s="57" t="inlineStr">
+      <c r="P3" s="57" t="inlineStr">
         <is>
           <t>2026-05-31	Current	4204
 2026-05-31	Full Payoff	678
@@ -3448,6 +3522,16 @@
 2026-05-31	150-179 DPD	1</t>
         </is>
       </c>
+      <c r="S3" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS FCL 同步表不存逾期状态（四维状态在 BPS 他处）</t>
+        </is>
+      </c>
+      <c r="T3" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1" s="74">
       <c r="A4" s="11" t="n">
@@ -3503,28 +3587,33 @@
           <t>DPD衍生计算基础</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="130" t="inlineStr">
+        <is>
+          <t>N/A — 不入 BPS FCL 同步表</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>✅ 100% (active FCL，MCP验证)</t>
         </is>
       </c>
-      <c r="M4" s="59" t="inlineStr">
+      <c r="N4" s="126" t="inlineStr">
         <is>
           <t>-- 验证 next_payment_due_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezpmt | 运行于: mysql_dev
 SELECT loanid, dataasof, nextduedate
 FROM   newrez.portnewrezpmt
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezpmt)
+WHERE  dataasof = '2026-06-01'
   AND  nextduedate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N4" s="68" t="inlineStr">
+      <c r="O4" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-06-01 | 2026-06-01 | 2026-07-01 | 2025-10-01 | 2024-07-01 | 2026-07-01 | 2026-06-01 | 2026-06-01 | 2026-07-01 | 2025-11-01（10笔）</t>
         </is>
       </c>
-      <c r="O4" s="57" t="inlineStr">
+      <c r="P4" s="57" t="inlineStr">
         <is>
           <t>700082700000027	2026-05-31	2026-06-01
 700082700000004	2026-05-31	2026-06-01
@@ -3538,6 +3627,16 @@
 700082700000013	2026-05-31	2025-11-01</t>
         </is>
       </c>
+      <c r="S4" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS FCL 同步表无此字段</t>
+        </is>
+      </c>
+      <c r="T4" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1" s="74">
       <c r="A5" s="12" t="n">
@@ -3593,25 +3692,40 @@
           <t>交叉验证 delinquency_status</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="L5" s="131" t="inlineStr">
+        <is>
+          <t>N/A — ETL 衍生 days360(nextduedate,dataasof)，不入 BPS FCL 同步表</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>N/A 衍生字段</t>
         </is>
       </c>
-      <c r="M5" s="60" t="inlineStr">
+      <c r="N5" s="127" t="inlineStr">
         <is>
           <t>-- N/A ETL衍生（days360(nextduedate,dataasof)）；替代验证源 nextduedate（最新快照取10笔样例）
 -- 源表: newrez.portnewrezpmt | 运行于: mysql_dev
 SELECT loanid, dataasof, nextduedate
 FROM   newrez.portnewrezpmt
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezpmt)
+WHERE  dataasof = '2026-06-01'
   AND  nextduedate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N5" s="68" t="inlineStr">
+      <c r="O5" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-06-01 | 2026-06-01 | 2026-07-01 | 2025-10-01 | 2024-07-01 | 2026-07-01 | 2026-06-01 | 2026-06-01 | 2026-07-01 | 2025-11-01（10笔）</t>
+        </is>
+      </c>
+      <c r="S5" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — ETL 衍生，BPS FCL 同步表无此字段</t>
+        </is>
+      </c>
+      <c r="T5" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -3669,31 +3783,46 @@
           <t>FCL入库条件 / BPS active_fcl_flag</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="130" t="inlineStr">
+        <is>
+          <t>N/A — 无 fcl_flag；FCL 活跃性见 active_fcl_flag→summary_completed_foreclosure</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>🟡 Newrez 无独立 fcl_flag 列（DB 实测）；FCL 活跃状态由 activefcflag 表达——最新快照实测 0/1 正常填充（非 null）。原"ETL 置 null"说法系针对不存在的 fcl_flag，已更正</t>
         </is>
       </c>
-      <c r="M6" s="61" t="inlineStr">
+      <c r="N6" s="128" t="inlineStr">
         <is>
           <t>-- N/A Newrez无fcl_flag列；FCL活跃状态由 activefcflag 表达
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT dataasof AS data_date, activefcflag, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
 GROUP  BY dataasof, activefcflag ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N6" s="68" t="inlineStr">
+      <c r="O6" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 0:5016 | 1:36</t>
         </is>
       </c>
-      <c r="O6" s="57" t="inlineStr">
+      <c r="P6" s="57" t="inlineStr">
         <is>
           <t>2026-05-31	0	5016
 2026-05-31	1	36</t>
+        </is>
+      </c>
+      <c r="S6" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 无 fcl_flag；活跃性见 active_fcl_flag→summary_completed_foreclosure</t>
+        </is>
+      </c>
+      <c r="T6" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -3751,34 +3880,39 @@
           <t>LM处理路由 / BPS LM Cycle面板路由</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="130" t="inlineStr">
+        <is>
+          <t>N/A — 无独立 flag；LM 存在性 = loss_mitigation 表是否有行</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>✅ 已提供（activelmflag，最新快照 100% 填充 0/1、无 null；实测 0:5018 | 1:34）。以 0/1 表达需映射 Y/N；为 LM 周期表层标志，类型/起止日见 lm_type / lm_start_date / lm_end_date</t>
         </is>
       </c>
-      <c r="M7" s="61" t="inlineStr">
+      <c r="N7" s="128" t="inlineStr">
         <is>
           <t>-- 验证 lm_flag 取值范围
 -- 源表: newrez.portnewrezlm | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, activelmflag, COUNT(*) AS cnt
 FROM   newrez.portnewrezlm
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezlm)
+WHERE  dataasof = '2026-06-01'
 GROUP  BY dataasof, activelmflag ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N7" s="68" t="inlineStr">
+      <c r="O7" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 0:5019 | 1:33</t>
         </is>
       </c>
-      <c r="O7" s="57" t="inlineStr">
+      <c r="P7" s="57" t="inlineStr">
         <is>
           <t>2026-05-31	0	5018
 2026-05-31	1	34</t>
         </is>
       </c>
-      <c r="P7" s="57" t="inlineStr">
+      <c r="Q7" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">
 select summary_foreclosure_status, COUNT(*) AS cnt
@@ -3786,7 +3920,7 @@
 GROUP  BY summary_foreclosure_status ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="Q7" s="57" t="inlineStr">
+      <c r="R7" s="57" t="inlineStr">
         <is>
           <t>Active Foreclosure	43
 Closed Foreclosure:Reinstated	21
@@ -3800,6 +3934,16 @@
 2. First Legal Filed	1</t>
         </is>
       </c>
+      <c r="S7" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 无独立 flag；LM 存在性=loss_mitigation 表是否有行</t>
+        </is>
+      </c>
+      <c r="T7" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="68" customHeight="1" s="74">
       <c r="A8" s="12" t="n">
@@ -3862,21 +4006,26 @@
           <t>LM类型路由</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="131" t="inlineStr">
+        <is>
+          <t>整数码 lmdeal 经 portnewrezdatadic 解码为文本（如 7→DIL）→ deal</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>❌ Newrez 不直接提供标准 lm_type 文本；以 lmdeal 整数码提供，ETL 解码为上述 8 个 deal（见 lm_deal 行；解码源 Redshift portnewrezdatadic）</t>
         </is>
       </c>
-      <c r="M8" s="66" t="inlineStr">
-        <is>
-          <t>-- 验证 lm_type 取值范围（lm_type ≡ lmdeal 解码后的 deal 大类；同时验证 Newrez 源 lmdeal 与 BPS 表 deal）
+      <c r="N8" s="120" t="inlineStr">
+        <is>
+          <t>-- 验证 lm_type 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
--- 运行于: mysql_bpms_dev（跨库 JOIN）| 解码源: Redshift portnewrezdatadic(LMDeal)，代码 basic_data_pool_config.py:835
+-- 运行于: mysql_bpms_dev（跨库 JOIN）| 详见 doc 数据字典 SQL-D1~D6
 -- 快照表：CTE 取每个 LM 周期的最新快照（latest-snapshot-per-cycle）
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, lmdeal,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE lmdeal IS NOT NULL
+  FROM newrez.portnewrezlm WHERE lmdeal IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.lmdeal, b.deal, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -3887,12 +4036,12 @@
 GROUP  BY l.lmdeal, b.deal ORDER BY l.lmdeal, cnt DESC;</t>
         </is>
       </c>
-      <c r="N8" s="68" t="inlineStr">
+      <c r="O8" s="68" t="inlineStr">
         <is>
           <t>1 Modification:194 | 1 Evaluation:2 | 2 Evaluation:104 | 4 Payment Plan:37 | 5 Forbearance:51 | 6 Short Sale:9 | 7 DIL:10 | 9 Payoff:1 | 11 Deferment:50</t>
         </is>
       </c>
-      <c r="O8" s="57" t="inlineStr">
+      <c r="P8" s="57" t="inlineStr">
         <is>
           <t>1	Modification	194
 1	Evaluation	2
@@ -3905,6 +4054,21 @@
 11	Deferment	50</t>
         </is>
       </c>
+      <c r="S8" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS deal 取值（dist）— 标准 lm_type ⇐ BPS deal（lmdeal 解码文本）
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `deal` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `deal` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T8" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Modification:207 | Evaluation:115 | ∅NULL:72 | Forbearance:57 | Deferment:56 | Payment Plan:39 | Short Sale:12 | DIL:10 | Payoff:1</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1" s="74">
       <c r="A9" s="12" t="n">
@@ -3960,25 +4124,45 @@
           <t>LM周期开始日</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（dealstartdate → cycle_opened_date）</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>🟡 周期级dealstartdate可用</t>
         </is>
       </c>
-      <c r="M9" s="61" t="inlineStr">
+      <c r="N9" s="128" t="inlineStr">
         <is>
           <t>-- 验证 lm_start_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezlm | 运行于: mysql_dev
 SELECT loanid, dataasof, dealstartdate
 FROM   newrez.portnewrezlm
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezlm)
+WHERE  dataasof = '2026-06-01'
   AND  dealstartdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N9" s="68" t="inlineStr">
+      <c r="O9" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-09-18 | 2026-04-28 | 2026-03-06 | 2025-07-18 | 2025-05-23 | 2025-09-19 | 2025-11-05 | 2025-12-10 | 2026-02-25 | 2026-03-31（10笔）</t>
+        </is>
+      </c>
+      <c r="S9" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS cycle_opened_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`cycle_opened_date`) AS non_null,
+       MIN(`cycle_opened_date`) AS min_dt, MAX(`cycle_opened_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation;</t>
+        </is>
+      </c>
+      <c r="T9" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 568/569 · 区间 2020-08-17~2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4036,25 +4220,45 @@
           <t>LM周期结束日</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（lmremovaldate → cycle_closed_date；NULL=进行中）</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>🟡 周期级lmremovaldate可用</t>
         </is>
       </c>
-      <c r="M10" s="61" t="inlineStr">
+      <c r="N10" s="128" t="inlineStr">
         <is>
           <t>-- 验证 lm_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezlm | 运行于: mysql_dev
 SELECT loanid, dataasof, lmremovaldate
 FROM   newrez.portnewrezlm
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezlm)
+WHERE  dataasof = '2026-06-01'
   AND  lmremovaldate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N10" s="68" t="inlineStr">
+      <c r="O10" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-07 | 2026-05-03 | 2026-05-08 | 2026-05-20 | 2025-12-03 | 2026-05-07 | 2026-05-01 | 2025-09-08 | 2025-05-27 | 2025-09-29（10笔）</t>
+        </is>
+      </c>
+      <c r="S10" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS cycle_closed_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`cycle_closed_date`) AS non_null,
+       MIN(`cycle_closed_date`) AS min_dt, MAX(`cycle_closed_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation;</t>
+        </is>
+      </c>
+      <c r="T10" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 511/569 · 区间 2020-09-22~2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4112,25 +4316,40 @@
           <t>Hold状态判断</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="131" t="inlineStr">
+        <is>
+          <t>N/A — 无独立 flag；Hold 存在性 = hold 表是否有行</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>❌ 无独立顶层标志（可从fchold1startdate推导）</t>
         </is>
       </c>
-      <c r="M11" s="62" t="inlineStr">
+      <c r="N11" s="120" t="inlineStr">
         <is>
           <t>-- N/A 无独立顶层 Hold flag；可从 fchold1startdate 推导（最新快照计数）
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
-SELECT MAX(dataasof) AS data_date, COUNT(*) AS hold_loans
+SELECT '2026-06-01' AS data_date, COUNT(*) AS hold_loans
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold1startdate IS NOT NULL;</t>
         </is>
       </c>
-      <c r="N11" s="68" t="inlineStr">
+      <c r="O11" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] hold_loans=89</t>
+        </is>
+      </c>
+      <c r="S11" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 无独立 flag；Hold 存在性=hold 表是否有行</t>
+        </is>
+      </c>
+      <c r="T11" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -4192,26 +4411,46 @@
           <t>Hold原因标准化</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" s="131" t="inlineStr">
+        <is>
+          <t>3 槽位 fchold1/2/3description UNPIVOT 合并 → description</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>❌ 自由文本（fchold1description：Loss Mitigation Workout | Court Delay 等，非标准枚举）</t>
         </is>
       </c>
-      <c r="M12" s="62" t="inlineStr">
+      <c r="N12" s="120" t="inlineStr">
         <is>
           <t>-- 验证 hold_reason 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, fchold1description AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold1description IS NOT NULL AND fchold1description != ''
 GROUP  BY dataasof, fchold1description ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N12" s="68" t="inlineStr">
+      <c r="O12" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Loss Mitigation Workout:21 | Awaiting Funds to Post:16 | Delinquency Review:12 | Bankruptcy Filed:6 | Hearing Set:4 | Court Delay:4 | Client Document Execution:4 | Service Delay:4 | Note Possession Confirmation:3 | Title Resolution:3 | Original Note:2 | Allonge of Note:1 | Service By Publication:1 | Guaranty Agreement:1 | Demand Letter Review:1 | Awaiting Escrow Analysis:1 | Moratorium:1 | Mediation Hearing:1 | FC Payment Research/Dispute:1 | ACT(PA) Letter/Demand Letter/NOI Expiration:1 | Original Assignment:1</t>
+        </is>
+      </c>
+      <c r="S12" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description 取值（dist）— 3 槽位 UNPIVOT 合并入 description
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `description` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_hold
+GROUP  BY `description` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T12" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Loss Mitigation Workout:63 | Service Delay:48 | ∅NULL:44 | Client Document Execution:29 | Court Delay:23 | Awaiting Funds to Post:20 | ACT(PA) Letter/Demand Letter/NOI Expiration:18 | Hearing Set:17 | Mediation Hearing:13 | Delinquency Review:11 | Original Note:10 | Title Resolution:9 | Note Possession Confirmation:8 | Bankruptcy Filed:8 | Copy of Power of Attorney:7 | Copy of Payment History:5 | Original Assignment:5 | Demand Letter Review:4 | Service By Publication:4 | Copy of Periodic Statement:4 | Pending Prior Servicer Doc(s):2 | Awaiting Escrow Analysis:2 | Soldiers and Sailors Relief Act:2 | Allonge of Note:2 | FC Payment Research/Dispute:2 | +15 个取值各1笔:15</t>
         </is>
       </c>
     </row>
@@ -4269,26 +4508,41 @@
           <t>REO状态标志</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
+        <is>
+          <t>N/A — 无独立 REO flag（可由 fcresults 间接识别）</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>❌ 0% (未提供)</t>
         </is>
       </c>
-      <c r="M13" s="62" t="inlineStr">
+      <c r="N13" s="120" t="inlineStr">
         <is>
           <t>-- N/A Newrez未提供独立 REO flag；可用 fcresults 间接识别
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT dataasof AS data_date, fcresults, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcresults IN ('REO','REO Sale')
 GROUP  BY dataasof, fcresults;</t>
         </is>
       </c>
-      <c r="N13" s="68" t="inlineStr">
+      <c r="O13" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] REO:6</t>
+        </is>
+      </c>
+      <c r="S13" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 无独立 REO flag</t>
+        </is>
+      </c>
+      <c r="T13" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -4346,25 +4600,40 @@
           <t>REO持有期计算</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="L14" s="131" t="inlineStr">
+        <is>
+          <t>N/A — 无独立 REO 取得日（可参考 dtdeedrecorded）</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>❌ 0% (未提供)</t>
         </is>
       </c>
-      <c r="M14" s="120" t="inlineStr">
+      <c r="N14" s="120" t="inlineStr">
         <is>
           <t>-- N/A Newrez未提供独立 REO 取得日；可参考 dtdeedrecorded=止赎契据登记日（成交后产权转让契据在县登记处登记=产权过户/止赎完成点，约在拍卖 fcsalehelddate 后 2-3 周，多数→REO），近似 REO 取得日（最新快照取10笔样例）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, dtdeedrecorded
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  dtdeedrecorded IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N14" s="68" t="inlineStr">
+      <c r="O14" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-28 | 2026-05-22 | 2025-10-28 | 2025-11-12（4笔）</t>
+        </is>
+      </c>
+      <c r="S14" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 无独立 REO 取得日列</t>
+        </is>
+      </c>
+      <c r="T14" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4653,7 @@
       <c r="I15" s="70" t="n"/>
       <c r="J15" s="71" t="n"/>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1" s="74">
       <c r="A16" s="11" t="n">
@@ -4440,25 +4709,46 @@
           <t>全部面板（全局JOIN主键）</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
+        <is>
+          <t>直接取值（loanid）</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M16" s="59" t="inlineStr">
+      <c r="N16" s="126" t="inlineStr">
         <is>
           <t>-- 验证 loan_id 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  loanid IS NOT NULL AND loanid != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N16" s="68" t="inlineStr">
+      <c r="O16" s="68" t="inlineStr">
         <is>
           <t>700082700000027 | 700082700000004 | 700082700000014 | 700082700000016 | 700082700000003 | 700082700000011 | 700082880000126 | 700082700000026 | 700082700000005 | 700082700000013（10行）</t>
+        </is>
+      </c>
+      <c r="S16" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS loanid 取值（idtext）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `loanid`
+FROM   bpms.sync_loan_foreclosure
+WHERE  `loanid` IS NOT NULL AND `loanid` != ''
+LIMIT  5;</t>
+        </is>
+      </c>
+      <c r="T16" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 样例(前5): 7727000012 | 7727000065 | 7727000082 | 7727000088 | 7727000119</t>
         </is>
       </c>
     </row>
@@ -4516,25 +4806,46 @@
           <t>FCL Summary &gt; summary_servicer_number</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
+        <is>
+          <t>直接取值（shellpointloanid → summary_servicer_number）</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M17" s="59" t="inlineStr">
+      <c r="N17" s="126" t="inlineStr">
         <is>
           <t>-- 验证 servicer_loan_id 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, shellpointloanid
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  shellpointloanid IS NOT NULL AND shellpointloanid != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N17" s="68" t="inlineStr">
+      <c r="O17" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 9799754446 | 9798424553 | 9796670868 | 9796285410 | 9792903412 | 9787544114 | 9779201442 | 9776836927 | 9776762263 | 9770660612（10笔）</t>
+        </is>
+      </c>
+      <c r="S17" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_servicer_number 取值（idtext）— =shellpointloanid
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_servicer_number`
+FROM   bpms.sync_loan_foreclosure
+WHERE  `summary_servicer_number` IS NOT NULL AND `summary_servicer_number` != ''
+LIMIT  5;</t>
+        </is>
+      </c>
+      <c r="T17" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 全为空（prod 未填充）</t>
         </is>
       </c>
     </row>
@@ -4592,25 +4903,40 @@
           <t>实时天数修正基础</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
+        <is>
+          <t>N/A — 主表无 dataasof 列（覆盖式快照）</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M18" s="59" t="inlineStr">
+      <c r="N18" s="126" t="inlineStr">
         <is>
           <t>-- 验证 data_as_of_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, dataasof
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  dataasof IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N18" s="68" t="inlineStr">
+      <c r="O18" s="68" t="inlineStr">
         <is>
           <t>700082700000027 | 700082700000004 | 700082700000014 | 700082700000016 | 700082700000003 | 700082700000011 | 700082880000126 | 700082700000026 | 700082700000005 | 700082700000013（10行）</t>
+        </is>
+      </c>
+      <c r="S18" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 主表无 dataasof 列（覆盖式快照）</t>
+        </is>
+      </c>
+      <c r="T18" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -4668,26 +4994,46 @@
           <t>阶段分类 / 目标天数配置</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
+        <is>
+          <t>直接取值（propertystate → sync_fcl_stage_info.state）</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M19" s="59" t="inlineStr">
+      <c r="N19" s="126" t="inlineStr">
         <is>
           <t>-- 验证 state 取值范围
 -- 源表: newrez.portnewrezprop | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, propertystate AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezprop
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezprop)
+WHERE  dataasof = '2026-06-01'
   AND  propertystate IS NOT NULL AND propertystate != ''
 GROUP  BY dataasof, propertystate ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N19" s="68" t="inlineStr">
+      <c r="O19" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] CA:794 | FL:617 | TX:395 | IL:331 | OH:257 | NY:210 | AZ:181 | NJ:167 | PA:167 | GA:159 | NC:158 | MN:137 | MI:107 | CO:101 | TN:99 | VA:97 | MD:86 | MO:84 | WA:79 | MA:77 | NV:75 | OR:65 | CT:65 | SC:65 | UT:53 | IN:47 | AL:46 | RI:38 | HI:29 | AR:27</t>
+        </is>
+      </c>
+      <c r="S19" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS state 取值（dist）— 主表无 state；BPS state 存于 sync_fcl_stage_info
+-- 表: bpms.sync_fcl_stage_info | 运行于: mysql_prod（只读）
+-- as-of: sync_fcl_stage_info 最新 fctrdt=2026-06-01；ETL 载入 update_time=2026-06-03
+SELECT '2026-06-01' AS data_date, `state` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_fcl_stage_info
+GROUP  BY `state` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T19" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt=2026-06-01·ETL载入 2026-06-03] FL:1510 | NY:1225 | IL:1075 | CA:983 | AZ:669 | IN:332 | TX:324 | CO:296 | PA:288 | WA:262 | OR:221 | MT:179 | MD:149 | NC:123 | OH:118 | MN:78 | MI:77 | NJ:74 | SC:70 | MA:68 | RI:55 | TN:47 | GA:40 | +其余州:0</t>
         </is>
       </c>
     </row>
@@ -4745,25 +5091,45 @@
           <t>FCL Summary &gt; summary_judicial_foreclosure / JUDGEMENT阶段路由</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
+        <is>
+          <t>judicial=1→'Judicial'，=0→'Non Judicial'，NULL→NULL（summary_type）；summary_judicial_foreclosure 直接取布尔</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M20" s="59" t="inlineStr">
+      <c r="N20" s="126" t="inlineStr">
         <is>
           <t>-- 验证 judicial_flag 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, judicial, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
 GROUP  BY dataasof, judicial ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N20" s="68" t="inlineStr">
+      <c r="O20" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] NULL:4953 | 0:51 | 1:48</t>
+        </is>
+      </c>
+      <c r="S20" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_judicial_foreclosure 取值（binary）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_judicial_foreclosure` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure
+GROUP  BY `summary_judicial_foreclosure` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T20" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 0:43 | 1:34 | ∅NULL:12</t>
         </is>
       </c>
     </row>
@@ -4821,25 +5187,45 @@
           <t>BPS入库条件（NULL-safe处理）</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="130" t="inlineStr">
+        <is>
+          <t>summary_completed_foreclosure = activefcflag 取反（=0→1，=1→0）；prod 实测该列全 NULL</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>✅ 100% (含历史NULL，需NULL-safe处理)</t>
         </is>
       </c>
-      <c r="M21" s="59" t="inlineStr">
+      <c r="N21" s="126" t="inlineStr">
         <is>
           <t>-- 验证 active_fcl_flag 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, activefcflag, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
 GROUP  BY dataasof, activefcflag ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N21" s="68" t="inlineStr">
+      <c r="O21" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 0:5016 | 1:36</t>
+        </is>
+      </c>
+      <c r="S21" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_completed_foreclosure 取值（binary）— BPS=activefcflag 取反；prod 实测全 NULL（异常，见结果）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_completed_foreclosure` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure
+GROUP  BY `summary_completed_foreclosure` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T21" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] ∅NULL:89</t>
         </is>
       </c>
     </row>
@@ -4897,25 +5283,45 @@
           <t>Timeline &gt; timeline_referred_to_foreclosure_date / BPS入库核心条件</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L22" s="130" t="inlineStr">
+        <is>
+          <t>直接取值（fcreferraldate → timeline_referred_to_foreclosure_date；入库过滤字段）</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M22" s="59" t="inlineStr">
+      <c r="N22" s="126" t="inlineStr">
         <is>
           <t>-- 验证 fcl_referral_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcreferraldate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcreferraldate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N22" s="68" t="inlineStr">
+      <c r="O22" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-02-18 | 2025-10-09 | 2026-05-26 | 2026-03-05 | 2026-01-28 | 2026-03-16 | 2026-01-29 | 2026-05-22 | 2026-05-26 | 2026-01-20（10笔）</t>
+        </is>
+      </c>
+      <c r="S22" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_referred_to_foreclosure_date 取值（date）— 入库过滤字段
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_referred_to_foreclosure_date`) AS non_null,
+       MIN(`timeline_referred_to_foreclosure_date`) AS min_dt, MAX(`timeline_referred_to_foreclosure_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T22" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 89/89 · 区间 2018-08-15~2026-05-27</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5341,7 @@
       <c r="I23" s="70" t="n"/>
       <c r="J23" s="71" t="n"/>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1" s="74">
       <c r="A24" s="12" t="n">
@@ -4991,26 +5397,46 @@
           <t>FCL Summary &gt; summary_current_step（备用，currentmilestone为空时使用）</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="L24" s="131" t="inlineStr">
+        <is>
+          <t>阶段瀑布判定（按里程碑优先级），存于 sync_fcl_stage_info.stage</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>✅ 99.5%</t>
         </is>
       </c>
-      <c r="M24" s="59" t="inlineStr">
+      <c r="N24" s="126" t="inlineStr">
         <is>
           <t>-- 验证 fcl_stage 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, fcstage AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcstage IS NOT NULL AND fcstage != ''
 GROUP  BY dataasof, fcstage ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N24" s="68" t="inlineStr">
+      <c r="O24" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Pre-Sale Review 1 (SCRA and PACER Check):16 | Service Complete:12 | Post Sale Review (SCRA and PACER Check):9 | Sale Scheduled For:9 | Title Report Received:7 | NOS Sent for Recording:6 | Complaint Sent for Filing:5 | Preliminary Title Clear:4 | Presale Redemption Will Expire On:3 | Pre-Sale Review 2 (SCRA and PACER Check):3 | Order Of Reference Sent:3 | Complaint Prepared and Sent for Filing:2 | Service Sent:2 | Judgment Hearing Scheduled For:2 | NOD Prepared and Sent for Filing :2 | NOD Mailed and Posted:1 | First Publication:1 | Order Of Reference Received:1 | Acceleration Letter Sent:1 | Hearing Complete:1 | TSG Report Received:1 | Dockets Prepared and Sent for Filing:1 | Is Home Equity/Judicial Rail Needed :1 | Return of Service Filed:1 | Answer Period Will Expire On:1 | Final Title Clear:1 | Complaint Submitted for Service:1 | Submitted for Service:1 | Notice …</t>
+        </is>
+      </c>
+      <c r="S24" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS stage 取值（dist）— BPS 阶段码存于 sync_fcl_stage_info.stage
+-- 表: bpms.sync_fcl_stage_info | 运行于: mysql_prod（只读）
+-- as-of: sync_fcl_stage_info 最新 fctrdt=2026-06-01；ETL 载入 update_time=2026-06-03
+SELECT '2026-06-01' AS data_date, `stage` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_fcl_stage_info
+GROUP  BY `stage` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T24" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt=2026-06-01·ETL载入 2026-06-03] REFERRAL:2738 | SALE:2068 | SERVICE:1528 | FIRST_LEGAL:775 | JUDGEMENT:732 | DEMAND:422</t>
         </is>
       </c>
     </row>
@@ -5074,26 +5500,46 @@
           <t>FCL Summary &gt; summary_current_step（最高优先级）</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="131" t="inlineStr">
+        <is>
+          <t>currentmilestone 非空则取之，否则取 fcstage（→ summary_current_step）</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>⚠️ 62.7% (低于可接受水平，建议提升至90%+)</t>
         </is>
       </c>
-      <c r="M25" s="61" t="inlineStr">
+      <c r="N25" s="128" t="inlineStr">
         <is>
           <t>-- 验证 current_milestone 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, currentmilestone AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  currentmilestone IS NOT NULL AND currentmilestone != ''
 GROUP  BY dataasof, currentmilestone ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N25" s="68" t="inlineStr">
+      <c r="O25" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Closed:54 | First Legal:16 | Sold:9 | Sale Held:7 | Service Complete:6 | Judgment Entered:4 | Sale Scheduled:3</t>
+        </is>
+      </c>
+      <c r="S25" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_current_step 取值（dist）— currentmilestone 否则 fcstage
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_current_step` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure
+GROUP  BY `summary_current_step` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T25" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] Pre-Sale Review 1 (SCRA and PACER Check):13 | Post Sale Review (SCRA and PACER Check):9 | NOS Sent for Recording:7 | Sale Scheduled For:7 | Service Complete:6 | Preliminary Title Clear:5 | ∅NULL:4 | Complaint Sent for Filing:3 | Order Of Reference Sent:3 | Pre-Sale Review 2 (SCRA and PACER Check):3 | First Legal Action Filed:2 | Title Summary:2 | Presale Redemption Will Expire On:2 | Pending First Legal:2 | Judgment Hearing Scheduled For:2 | NOD Prepared and Sent for Filing :2 | Title Report Received:2 | Return of Service Filed:1 | Acceleration Letter Sent:1 | Is Home Equity/Judicial Rail Needed :1 | Order Of Reference Received:1 | Hearing Complete:1 | TSG Report Received:1 | Complaint Submitted for Service:1 | Contested / Litigation Start:1 | Sale Deed Recorded:1 | Dockets Prepared and Sent for Filing:1 | Answer Period …</t>
         </is>
       </c>
     </row>
@@ -5151,26 +5597,46 @@
           <t>FCL Summary &gt; summary_last_step_completed</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="L26" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（lastfcstepcompleted → summary_last_step_completed）</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>✅ 99.5%</t>
         </is>
       </c>
-      <c r="M26" s="59" t="inlineStr">
+      <c r="N26" s="126" t="inlineStr">
         <is>
           <t>-- 验证 last_completed_step 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, lastfcstepcompleted AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  lastfcstepcompleted IS NOT NULL AND lastfcstepcompleted != ''
 GROUP  BY dataasof, lastfcstepcompleted ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N26" s="68" t="inlineStr">
+      <c r="O26" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Preliminary Title Clear:21 | Post Sale Review (SCRA and PACER Check):9 | File Received By Attorney:8 | Sale Scheduled For:6 | Complaint Sent For Service:5 | Title Report Received:4 | Submitted for Service:4 | Presale Redemption Will Expire On:3 | NOS Recorded:3 | Answer Period Will Expire On:3 | Final Title Clear:3 | NOS Posted:3 | HUD First Action Expires:2 | Review for Judicial Action:2 | Motion for Judgment Sent to Court:2 | NOS Sent for Recording:2 | Complaint Submitted for Service:2 | Firm Registers NOI With State:2 | Service Complete:2 | NOTS Recorded:1 | Complaint Filed:1 | File Referred To Attorney:1 | First Publication of NOS:1 | Order Authorizing Sale Received:1 | Attorney Acknowledges:1 | Praecipe Filed:1 | Hearing Scheduled For:1 | NOD Filed:1 | Are We Proceeding with a Consent Judgment :1 | Order Of Reference Sent:1</t>
+        </is>
+      </c>
+      <c r="S26" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_last_step_completed 取值（dist）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_last_step_completed` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure
+GROUP  BY `summary_last_step_completed` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T26" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] Preliminary Title Clear:12 | ∅NULL:12 | Post Sale Review (SCRA and PACER Check):9 | Title Report Received:5 | Sale Scheduled For:5 | NOS Recorded:3 | File Received By Attorney:3 | Submitted for Service:3 | Final Title Clear:3 | Answer Period Will Expire On:3 | Presale Redemption Will Expire On:3 | Motion for Judgment Sent to Court:2 | NOS Sent for Recording:2 | Review for Judicial Action:2 | Service Complete:2 | Complaint Sent For Service:2 | HUD First Action Expires:2 | NOTS Recorded:1 | First Publication:1 | Hearing Scheduled For:1 | Order Of Reference Sent:1 | NOD Filed:1 | Praecipe Filed:1 | Is Home Equity/Judicial Rail Needed :1 | First Publication of NOS:1 | Are We Proceeding with a Consent Judgment :1 | Order Authorizing Sale Received:1 | NOS Posted:1 | Complaint Submitted for Service:1 | Complaint Filed:1 | Firm …</t>
         </is>
       </c>
     </row>
@@ -5228,25 +5694,45 @@
           <t>FCL Summary &gt; summary_last_step_completed_date</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L27" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（lastfcstepcompleteddate → summary_last_step_completed_date）</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>✅ 99.5%</t>
         </is>
       </c>
-      <c r="M27" s="59" t="inlineStr">
+      <c r="N27" s="126" t="inlineStr">
         <is>
           <t>-- 验证 last_completed_step_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, lastfcstepcompleteddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  lastfcstepcompleteddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N27" s="68" t="inlineStr">
+      <c r="O27" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-02-26 | 2025-11-03 | 2026-05-26 | 2026-04-23 | 2026-05-05 | 2026-04-30 | 2026-03-03 | 2026-05-22 | 2026-05-26 | 2026-03-13（10笔）</t>
+        </is>
+      </c>
+      <c r="S27" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_last_step_completed_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`summary_last_step_completed_date`) AS non_null,
+       MIN(`summary_last_step_completed_date`) AS min_dt, MAX(`summary_last_step_completed_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T27" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 77/89 · 区间 2019-10-14~2026-05-26</t>
         </is>
       </c>
     </row>
@@ -5304,26 +5790,41 @@
           <t>FCL Summary（已完成贷款）/ timeline_third_party_sold_date触发</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="L28" s="131" t="inlineStr">
+        <is>
+          <t>N/A — BPS 不单独存；仅参与 fcresults='3rd Party' 的 timeline_third_party_sold 判断</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>⚠️ 2.1% (仅完成贷款，部分填充属正常)</t>
         </is>
       </c>
-      <c r="M28" s="61" t="inlineStr">
+      <c r="N28" s="128" t="inlineStr">
         <is>
           <t>-- 验证 fcl_results 取值范围
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, fcresults AS val, COUNT(*) AS cnt
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcresults IS NOT NULL AND fcresults != ''
 GROUP  BY dataasof, fcresults ORDER BY cnt DESC LIMIT 30;</t>
         </is>
       </c>
-      <c r="N28" s="68" t="inlineStr">
+      <c r="O28" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] REO:6 | 3rd Party:3</t>
+        </is>
+      </c>
+      <c r="S28" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS 不单独存 fcresults（仅用于 Foreclosure Status 文本/REO 识别）</t>
+        </is>
+      </c>
+      <c r="T28" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -5338,144 +5839,180 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
+          <t>fcl_removal_description</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezfc.fcremovaldesc</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>退出/关闭止赎流程的原因（仅已退出 FCL 的贷款有值）；驱动 BPS Foreclosure Status 的 'Closed Foreclosure: &lt;desc&gt;' 后缀；与 fcl_removal_date（退出日期）配对</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>文本枚举（Newrez 直接取值 fcremovaldesc）</t>
+        </is>
+      </c>
+      <c r="I29" s="48" t="inlineStr">
+        <is>
+          <t>Reinstated | Loss Mitigation | Paid in Full | Process Complete | Deed in Lieu Cmplte（活跃 FCL 为空）</t>
+        </is>
+      </c>
+      <c r="J29" s="48" t="inlineStr">
+        <is>
+          <t>Reinstated</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>FCL Summary &gt; summary_foreclosure_status（并入 'Closed Foreclosure:'+desc；BPS 无独立列）</t>
+        </is>
+      </c>
+      <c r="L29" s="131" t="inlineStr">
+        <is>
+          <t>N/A — 不单独存；并入 summary_foreclosure_status（activefcflag=0 且非空时 = 'Closed Foreclosure:'+fcremovaldesc）</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>✅ ~1.2%（仅已退出 FCL 贷款；实测 2026-06-01 共 63 笔非空，5 个取值）</t>
+        </is>
+      </c>
+      <c r="N29" s="128" t="inlineStr">
+        <is>
+          <t>-- 验证 fcl_removal_description 取值范围
+-- 源表: newrez.portnewrezfc | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, fcremovaldesc AS val, COUNT(*) AS cnt
+FROM   newrez.portnewrezfc
+WHERE  dataasof = '2026-06-01'
+  AND  fcremovaldesc IS NOT NULL AND fcremovaldesc != ''
+GROUP  BY dataasof, fcremovaldesc ORDER BY cnt DESC LIMIT 30;</t>
+        </is>
+      </c>
+      <c r="O29" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] Reinstated:26 | Loss Mitigation:16 | Paid in Full:11 | Process Complete:9 | Deed in Lieu Cmplte:1</t>
+        </is>
+      </c>
+      <c r="S29" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS 不单独存；并入 summary_foreclosure_status 文本（'Closed Foreclosure:'+fcremovaldesc）</t>
+        </is>
+      </c>
+      <c r="T29" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1" s="74">
+      <c r="A30" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>2.2 FCL状态字段 — P1，FC</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
           <t>attorney_firm</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcfirm</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>处理此止赎案件的律师事务所全名</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>律师事务所名称文本</t>
         </is>
       </c>
-      <c r="I29" s="48" t="inlineStr">
+      <c r="I30" s="48" t="inlineStr">
         <is>
           <t>自由文本（律师事务所名称）</t>
         </is>
       </c>
-      <c r="J29" s="48" t="inlineStr">
+      <c r="J30" s="48" t="inlineStr">
         <is>
           <t>Kelley Kronenberg, P.A.</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>FCL Summary &gt; summary_foreclosure_attorney / summary_firm</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="L30" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fcfirm → summary_foreclosure_attorney / summary_firm）</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M29" s="59" t="inlineStr">
+      <c r="N30" s="126" t="inlineStr">
         <is>
           <t>-- 验证 attorney_firm 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcfirm
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcfirm IS NOT NULL AND fcfirm != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N29" s="68" t="inlineStr">
+      <c r="O30" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Korde &amp; Associates, P.C. | Stern &amp; Eisenberg, PC | Padgett Law Group | Clunk, Hoose Co., LPA | Friedman Vartolo LLP  | McCarthy &amp; Holthus, LLP | Friedman Vartolo LLP  | McCarthy &amp; Holthus, LLP | Foundation Legal Group, LLP | Friedman Vartolo LLP （10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="40" customHeight="1" s="74">
-      <c r="A30" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>2.2 FCL状态字段 — P1，FC</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>contested_flag</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezfc.fccontestedflag</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>TINYINT</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>是否存在争议诉讼（借款人提出法律异议）</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>0=无争议 / 1=有争议</t>
-        </is>
-      </c>
-      <c r="I30" s="48" t="inlineStr">
-        <is>
-          <t>0 / 1</t>
-        </is>
-      </c>
-      <c r="J30" s="48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>FCL Summary &gt; summary_contested_litigation</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>✅ 100%</t>
-        </is>
-      </c>
-      <c r="M30" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 contested_flag 取值范围
--- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, fccontestedflag, COUNT(*) AS cnt
-FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
-GROUP  BY dataasof, fccontestedflag ORDER BY cnt DESC;</t>
-        </is>
-      </c>
-      <c r="N30" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] 0:5051 | 1:1</t>
+      <c r="S30" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_foreclosure_attorney 取值（dist）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_foreclosure_attorney` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure
+GROUP  BY `summary_foreclosure_attorney` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T30" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] ∅NULL:85 | Brock &amp; Scott PLLC:1 | McPhail Sanchez, LLC:1 | Vylla Solutions, LLC:1 | Lender Legal PLLC:1</t>
         </is>
       </c>
     </row>
@@ -5490,688 +6027,874 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
+          <t>contested_flag</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezfc.fccontestedflag</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>TINYINT</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>是否存在争议诉讼（借款人提出法律异议）</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>0=无争议 / 1=有争议</t>
+        </is>
+      </c>
+      <c r="I31" s="48" t="inlineStr">
+        <is>
+          <t>0 / 1</t>
+        </is>
+      </c>
+      <c r="J31" s="48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>FCL Summary &gt; summary_contested_litigation</t>
+        </is>
+      </c>
+      <c r="L31" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fccontestedflag → summary_contested_litigation）</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>✅ 100%</t>
+        </is>
+      </c>
+      <c r="N31" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 contested_flag 取值范围
+-- 源表: newrez.portnewrezfc | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, fccontestedflag, COUNT(*) AS cnt
+FROM   newrez.portnewrezfc
+WHERE  dataasof = '2026-06-01'
+GROUP  BY dataasof, fccontestedflag ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="O31" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] 0:5051 | 1:1</t>
+        </is>
+      </c>
+      <c r="S31" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_contested_litigation 取值（binary）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, `summary_contested_litigation` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure
+GROUP  BY `summary_contested_litigation` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T31" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 0:75 | ∅NULL:13 | 1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1" s="74">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>2.2 FCL状态字段 — P1，FC</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
           <t>servicer_days_in_fcl</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.smsdaysinfc</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Servicer 口径的 FCL 在途天数（Newrez/SMS=Shellpoint Mortgage Servicing 实现为原生 smsdaysinfc / ETL 别名 svc_days_infc，透传），自 servicer 建案日 fcsetupdate 起算。BPS 实时修正：smsdaysinfc + DATEDIFF(今日纽约, dataasof)。因 setup≥referral，故 ≤ days_in_fcl（投资人全程口径）。注：标准接口字段名取 servicer-中性名 servicer_days_in_fcl；smsdaysinfc/summary_sms_days_in_fcl 为 Newrez/BPS 真实列名</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>正整数（以dataasof为基准）</t>
         </is>
       </c>
-      <c r="I31" s="48" t="inlineStr">
+      <c r="I32" s="48" t="inlineStr">
         <is>
           <t>正整数</t>
         </is>
       </c>
-      <c r="J31" s="48" t="inlineStr">
+      <c r="J32" s="48" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>FCL Summary &gt; summary_sms_days_in_fcl</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L32" s="131" t="inlineStr">
+        <is>
+          <t>原值 smsdaysinfc + DATEDIFF(今日纽约, dataasof) 实时重算（自 fcsetupdate 起算）</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>✅ 100%（smsdaysinfc，1~606天）</t>
         </is>
       </c>
-      <c r="M31" s="59" t="inlineStr">
+      <c r="N32" s="126" t="inlineStr">
         <is>
           <t>-- 验证 servicer_days_in_fcl 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, smsdaysinfc
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  smsdaysinfc IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N31" s="68" t="inlineStr">
+      <c r="O32" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 10 | 29 | 7 | 67 | 99 | 50 | 40 | 11 | 7 | 133（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="40" customHeight="1" s="74">
-      <c r="A32" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="S32" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_sms_days_in_fcl 取值（numeric）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`summary_sms_days_in_fcl`) AS non_null,
+       MIN(`summary_sms_days_in_fcl`) AS min_v, MAX(`summary_sms_days_in_fcl`) AS max_v, ROUND(AVG(`summary_sms_days_in_fcl`),2) AS avg_v
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T32" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 69/89 · 区间 9~610 · 均值 188.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="74">
+      <c r="A33" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>2.2 FCL状态字段 — P1，FC</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>days_in_fcl</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.daysinfc</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>投资人 / 全程视角的 FCL 在途天数。ETL 按 fcreferraldate（转介日）重算：datediff(referral_start_date, snapshot)+1（仅 Active；basic_data_pool_config.py:1628）。与 servicer_days_in_fcl 的区别=起算基准不同（referral vs setup），故 days_in_fcl ≥ servicer_days_in_fcl；BPS 同样 + DATEDIFF(今日纽约, dataasof) 实时修正</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>正整数（以dataasof为基准）</t>
         </is>
       </c>
-      <c r="I32" s="48" t="inlineStr">
+      <c r="I33" s="48" t="inlineStr">
         <is>
           <t>正整数</t>
         </is>
       </c>
-      <c r="J32" s="48" t="inlineStr">
+      <c r="J33" s="48" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>FCL Summary &gt; summary_days_in_fcl</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L33" s="131" t="inlineStr">
+        <is>
+          <t>原值 daysinfc + DATEDIFF(今日纽约, dataasof) 实时重算（自 fcreferraldate 起算）</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>✅ 100%（daysinfc，1~814天）</t>
         </is>
       </c>
-      <c r="M32" s="59" t="inlineStr">
+      <c r="N33" s="126" t="inlineStr">
         <is>
           <t>-- 验证 days_in_fcl 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, daysinfc
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  daysinfc IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N32" s="68" t="inlineStr">
+      <c r="O33" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 10 | 29 | 7 | 67 | 99 | 50 | 40 | 11 | 7 | 133（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" s="74">
-      <c r="A33" s="119" t="inlineStr">
+      <c r="S33" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_days_in_fcl 取值（numeric）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`summary_days_in_fcl`) AS non_null,
+       MIN(`summary_days_in_fcl`) AS min_v, MAX(`summary_days_in_fcl`) AS max_v, ROUND(AVG(`summary_days_in_fcl`),2) AS avg_v
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T33" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 83/89 · 区间 8~818 · 均值 185.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="74">
+      <c r="A34" s="119" t="inlineStr">
         <is>
           <t>Section 2.3 — FCL时间轴字段 — Timeline面板 + 聚合Time Line Tab</t>
         </is>
       </c>
-      <c r="B33" s="70" t="n"/>
-      <c r="C33" s="70" t="n"/>
-      <c r="D33" s="70" t="n"/>
-      <c r="E33" s="70" t="n"/>
-      <c r="F33" s="70" t="n"/>
-      <c r="G33" s="70" t="n"/>
-      <c r="H33" s="70" t="n"/>
-      <c r="I33" s="70" t="n"/>
-      <c r="J33" s="71" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="3" t="n"/>
-    </row>
-    <row r="34" ht="40" customHeight="1" s="74">
-      <c r="A34" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="70" t="n"/>
+      <c r="C34" s="70" t="n"/>
+      <c r="D34" s="70" t="n"/>
+      <c r="E34" s="70" t="n"/>
+      <c r="F34" s="70" t="n"/>
+      <c r="G34" s="70" t="n"/>
+      <c r="H34" s="70" t="n"/>
+      <c r="I34" s="70" t="n"/>
+      <c r="J34" s="71" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="M34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="40" customHeight="1" s="74">
+      <c r="A35" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>noi_date</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>— (Newrez以newrez.portnewrezfc.demandsentdate代替，无专用NOI字段)</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>各州法律要求的正式止赎意向通知（NOI）日期；与demandsentdate（催款函）概念不同；Newrez将两者合并，BPS以demandsentdate临时代替</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；Newrez以demandsentdate临时代替</t>
         </is>
       </c>
-      <c r="I34" s="48" t="inlineStr">
+      <c r="I35" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J34" s="48" t="inlineStr">
+      <c r="J35" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K34" s="12" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_notice_of_intent_date / Time Line Tab &gt; noi_start_date</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="L35" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（demandsentdate → timeline_notice_of_intent_date）</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>❌ 未单独提供（BPS以demandsentdate临时代替）</t>
         </is>
       </c>
-      <c r="M34" s="62" t="inlineStr">
+      <c r="N35" s="120" t="inlineStr">
         <is>
           <t>-- N/A Newrez未单独提供 NOI；BPS 以 demandsentdate 代替（最新快照取10笔样例）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, demandsentdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  demandsentdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N34" s="68" t="inlineStr">
+      <c r="O35" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2024-12-05 | 2026-04-15 | 2025-06-16 | 2026-04-17 | 2026-05-29 | 2026-04-13 | 2026-01-22 | 2026-05-04 | 2025-11-24 | 2025-12-19（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="40" customHeight="1" s="74">
-      <c r="A35" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="S35" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_notice_of_intent_date 取值（date）— 源 demandsentdate
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_notice_of_intent_date`) AS non_null,
+       MIN(`timeline_notice_of_intent_date`) AS min_dt, MAX(`timeline_notice_of_intent_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T35" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 5/89 · 区间 2024-05-17~2025-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1" s="74">
+      <c r="A36" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>demand_sent_date</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.demandsentdate</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>止赎前催款函/违约通知发出日期；触发BPS DEMAND阶段分类</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I35" s="48" t="inlineStr">
+      <c r="I36" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J35" s="48" t="inlineStr">
+      <c r="J36" s="48" t="inlineStr">
         <is>
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr">
+      <c r="K36" s="12" t="inlineStr">
         <is>
           <t>DEMAND阶段分类触发 / demand_start_date（聚合页）</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L36" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（demandsentdate → timeline_notice_of_intent_date；同 noi_date）</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>✅ 85.9%（demandsentdate，2021-10-18~2026-04-20，见doc 13 Q5）</t>
         </is>
       </c>
-      <c r="M35" s="59" t="inlineStr">
+      <c r="N36" s="126" t="inlineStr">
         <is>
           <t>-- 验证 demand_sent_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, demandsentdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  demandsentdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N35" s="68" t="inlineStr">
+      <c r="O36" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2024-12-05 | 2026-04-15 | 2025-06-16 | 2026-04-17 | 2026-05-29 | 2026-04-13 | 2026-01-22 | 2026-05-04 | 2025-11-24 | 2025-12-19（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="40" customHeight="1" s="74">
-      <c r="A36" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="S36" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_notice_of_intent_date 取值（date）— 同 noi_date（源 demandsentdate）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_notice_of_intent_date`) AS non_null,
+       MIN(`timeline_notice_of_intent_date`) AS min_dt, MAX(`timeline_notice_of_intent_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T36" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 5/89 · 区间 2024-05-17~2025-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1" s="74">
+      <c r="A37" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>demand_expiration_date</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.demandexpirationdate</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>NOI/催款函到期日；计算：actual_notice_of_intent_days = demandexpirationdate − demandsentdate</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I36" s="48" t="inlineStr">
+      <c r="I37" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J36" s="48" t="inlineStr">
+      <c r="J37" s="48" t="inlineStr">
         <is>
           <t>2024-03-02</t>
         </is>
       </c>
-      <c r="K36" s="12" t="inlineStr">
+      <c r="K37" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_notice_of_intent_end_date</t>
         </is>
       </c>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="L37" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（demandexpirationdate → timeline_notice_of_intent_end_date）</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>✅ 85.7%</t>
         </is>
       </c>
-      <c r="M36" s="59" t="inlineStr">
+      <c r="N37" s="126" t="inlineStr">
         <is>
           <t>-- 验证 demand_expiration_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, demandexpirationdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  demandexpirationdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N36" s="68" t="inlineStr">
+      <c r="O37" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-02-08 | 2026-05-20 | 2025-12-19 | 2026-05-17 | 2026-06-13 | 2026-04-28 | 2026-02-21 | 2026-05-20 | 2025-12-19 | 2026-01-18（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="40" customHeight="1" s="74">
-      <c r="A37" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="S37" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_notice_of_intent_end_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_notice_of_intent_end_date`) AS non_null,
+       MIN(`timeline_notice_of_intent_end_date`) AS min_dt, MAX(`timeline_notice_of_intent_end_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T37" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 0/89（prod 全空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1" s="74">
+      <c r="A38" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>fcl_setup_date</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcsetupdate</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>FCL内部开设日期（BPS系统建案日）；Newrez通常与fcreferraldate同一日期</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I37" s="48" t="inlineStr">
+      <c r="I38" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J37" s="48" t="inlineStr">
+      <c r="J38" s="48" t="inlineStr">
         <is>
           <t>2024-01-10</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
+      <c r="K38" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_approved_for_referral_date</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L38" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fcsetupdate → timeline_approved_for_referral_date）</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>✅ 100%（fcsetupdate，2024-02-07~2026-05-26）</t>
         </is>
       </c>
-      <c r="M37" s="59" t="inlineStr">
+      <c r="N38" s="126" t="inlineStr">
         <is>
           <t>-- 验证 fcl_setup_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcsetupdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcsetupdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N37" s="68" t="inlineStr">
+      <c r="O38" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-02-18 | 2025-10-09 | 2026-05-26 | 2026-03-05 | 2026-01-28 | 2026-03-16 | 2026-01-29 | 2026-05-22 | 2026-05-26 | 2026-01-20（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="40" customHeight="1" s="74">
-      <c r="A38" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="S38" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_approved_for_referral_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_approved_for_referral_date`) AS non_null,
+       MIN(`timeline_approved_for_referral_date`) AS min_dt, MAX(`timeline_approved_for_referral_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T38" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 0/89（prod 全空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1" s="74">
+      <c r="A39" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>first_legal_date</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.firstlegaldate</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>止赎诉讼首次向法院提起的日期；Non-Judicial州通常为空；触发FIRST_LEGAL阶段</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；Non-Judicial州可为空</t>
         </is>
       </c>
-      <c r="I38" s="48" t="inlineStr">
+      <c r="I39" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J38" s="48" t="inlineStr">
+      <c r="J39" s="48" t="inlineStr">
         <is>
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr">
+      <c r="K39" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_first_legal_date / FIRST_LEGAL阶段</t>
         </is>
       </c>
-      <c r="L38" s="8" t="inlineStr">
+      <c r="L39" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（firstlegaldate → timeline_first_legal_date；非司法州常空）</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
         <is>
           <t>⚠️ 57.6% (Non-Judicial州部分预期为空)</t>
         </is>
       </c>
-      <c r="M38" s="61" t="inlineStr">
+      <c r="N39" s="128" t="inlineStr">
         <is>
           <t>-- 验证 first_legal_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, firstlegaldate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  firstlegaldate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N38" s="68" t="inlineStr">
+      <c r="O39" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-23 | 2026-04-28 | 2026-04-30 | 2026-02-25 | 2026-03-12 | 2025-10-30 | 2026-04-28 | 2026-05-28 | 2025-08-19 | 2026-02-19（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="40" customHeight="1" s="74">
-      <c r="A39" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="S39" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_first_legal_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_first_legal_date`) AS non_null,
+       MIN(`timeline_first_legal_date`) AS min_dt, MAX(`timeline_first_legal_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T39" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 47/89 · 区间 2018-10-29~2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1" s="74">
+      <c r="A40" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>service_complete_date</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.servicecompletedate</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>法律文件成功送达借款人的日期；触发SERVICE阶段</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I39" s="48" t="inlineStr">
+      <c r="I40" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J39" s="48" t="inlineStr">
+      <c r="J40" s="48" t="inlineStr">
         <is>
           <t>2024-03-10</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr">
+      <c r="K40" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_service_date / SERVICE阶段</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="L40" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（servicecompletedate → timeline_service_date）</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
         <is>
           <t>⚠️ 28.9% (早期阶段贷款预期为空)</t>
         </is>
       </c>
-      <c r="M39" s="61" t="inlineStr">
+      <c r="N40" s="128" t="inlineStr">
         <is>
           <t>-- 验证 service_complete_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, servicecompletedate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  servicecompletedate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N39" s="68" t="inlineStr">
+      <c r="O40" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2024-11-26 | 2025-05-23 | 2024-04-01 | 2025-11-19 | 2025-03-04 | 2025-08-14 | 2025-06-02 | 2025-07-18 | 2026-01-13 | 2025-05-03（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="40" customHeight="1" s="74">
-      <c r="A40" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>2.3 FCL时间轴字段 — Time</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>publication_date</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
-        <is>
-          <t>— (无对应字段，Newrez未提供)</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>止赎通知在报纸/官方渠道发布的日期（Non-Judicial州必要步骤）；Newrez不提供</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="I40" s="49" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="J40" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>Timeline &gt; timeline_publication_date / PUBLICATION阶段</t>
-        </is>
-      </c>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>❌ 0% (Newrez未提供，见doc 13 Q1)</t>
-        </is>
-      </c>
-      <c r="M40" s="62" t="inlineStr">
-        <is>
-          <t>-- N/A — Newrez未提供（无可验证源）</t>
-        </is>
-      </c>
-      <c r="N40" s="68" t="inlineStr">
-        <is>
-          <t>N/A（无可验证源）</t>
+      <c r="S40" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_service_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_service_date`) AS non_null,
+       MIN(`timeline_service_date`) AS min_dt, MAX(`timeline_service_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T40" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 19/89 · 区间 2018-12-10~2026-02-16</t>
         </is>
       </c>
     </row>
@@ -6186,773 +6909,961 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
+          <t>publication_date</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>— (无对应字段，Newrez未提供)</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>止赎通知在报纸/官方渠道发布的日期（Non-Judicial州必要步骤）；Newrez不提供</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="I41" s="49" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="J41" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Timeline &gt; timeline_publication_date / PUBLICATION阶段</t>
+        </is>
+      </c>
+      <c r="L41" s="132" t="inlineStr">
+        <is>
+          <t>Newrez 未提供，timeline_publication_date 恒空</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>❌ 0% (Newrez未提供，见doc 13 Q1)</t>
+        </is>
+      </c>
+      <c r="N41" s="120" t="inlineStr">
+        <is>
+          <t>-- N/A — Newrez未提供（无可验证源）</t>
+        </is>
+      </c>
+      <c r="O41" s="68" t="inlineStr">
+        <is>
+          <t>N/A（无可验证源）</t>
+        </is>
+      </c>
+      <c r="S41" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_publication_date 取值（date）— Newrez 未提供，预期恒空
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_publication_date`) AS non_null,
+       MIN(`timeline_publication_date`) AS min_dt, MAX(`timeline_publication_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T41" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 0/89（prod 全空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1" s="74">
+      <c r="A42" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>2.3 FCL时间轴字段 — Time</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
           <t>title_received_date</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.titlereceiveddate</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>律师事务所收到产权调查报告的日期；Newrez字段存在但始终为空</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I41" s="49" t="inlineStr">
+      <c r="I42" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J41" s="49" t="inlineStr">
+      <c r="J42" s="49" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="K41" s="13" t="inlineStr">
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_title_report_received_date</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr">
+      <c r="L42" s="132" t="inlineStr">
+        <is>
+          <t>直接取值（titlereceiveddate → timeline_title_report_received_date；Newrez 多为空）</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>❌ 0% (字段存在但始终为空，见doc 13 Q8)</t>
         </is>
       </c>
-      <c r="M41" s="62" t="inlineStr">
+      <c r="N42" s="120" t="inlineStr">
         <is>
           <t>-- 验证 title_received_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, titlereceiveddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  titlereceiveddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N41" s="68" t="inlineStr">
+      <c r="O42" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-26 | 2025-12-02 | 2025-03-24 | 2025-12-02（4笔）</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="40" customHeight="1" s="74">
-      <c r="A42" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="S42" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_title_report_received_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_title_report_received_date`) AS non_null,
+       MIN(`timeline_title_report_received_date`) AS min_dt, MAX(`timeline_title_report_received_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T42" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 4/89 · 区间 2025-03-24~2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1" s="74">
+      <c r="A43" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>title_clear_date</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.titlecleardate</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>产权调查确认无未知留置权的日期；同时适用于初步和最终产权清除；Newrez不提供</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I42" s="49" t="inlineStr">
+      <c r="I43" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J42" s="49" t="inlineStr">
+      <c r="J43" s="49" t="inlineStr">
         <is>
           <t>2025-04-15</t>
         </is>
       </c>
-      <c r="K42" s="13" t="inlineStr">
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>Timeline &gt; 初步/最终产权清除日期</t>
         </is>
       </c>
-      <c r="L42" s="6" t="inlineStr">
+      <c r="L43" s="132" t="inlineStr">
+        <is>
+          <t>直接取值（titlecleardate → timeline_preliminary_title_cleared_date / final_title_cleared）</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
         <is>
           <t>❌ 0% (字段存在但始终为空，见doc 13 Q8)</t>
         </is>
       </c>
-      <c r="M42" s="62" t="inlineStr">
+      <c r="N43" s="120" t="inlineStr">
         <is>
           <t>-- 验证 title_clear_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, titlecleardate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  titlecleardate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N42" s="68" t="inlineStr">
+      <c r="O43" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-26 | 2025-03-24 | 2026-02-02（3笔）</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="40" customHeight="1" s="74">
-      <c r="A43" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="S43" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_preliminary_title_cleared_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_preliminary_title_cleared_date`) AS non_null,
+       MIN(`timeline_preliminary_title_cleared_date`) AS min_dt, MAX(`timeline_preliminary_title_cleared_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T43" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 3/89 · 区间 2025-03-24~2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1" s="74">
+      <c r="A44" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>judgement_hearing_scheduled</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcjudgmenthearingscheduled</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>止赎判决听证会的计划日期（未来计划事件）；仅Judicial州；触发JUDGEMENT阶段（优先级2）；ETL代码确认：fcjudgment_hearing_scheduled AS timeline_judgement_date</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；仅Judicial州</t>
         </is>
       </c>
-      <c r="I43" s="48" t="inlineStr">
+      <c r="I44" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD（Judicial州）</t>
         </is>
       </c>
-      <c r="J43" s="48" t="inlineStr">
+      <c r="J44" s="48" t="inlineStr">
         <is>
           <t>2026-01-18</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K44" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_judgement_date / judgement_start_date（聚合页）/ JUDGEMENT阶段</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L44" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fcjudgmenthearingscheduled → timeline_judgement_hearing_set_date / timeline_judgement_date）</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>✅ 11.9% (仅Judicial州)</t>
         </is>
       </c>
-      <c r="M43" s="59" t="inlineStr">
+      <c r="N44" s="126" t="inlineStr">
         <is>
           <t>-- 验证 judgement_hearing_scheduled 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcjudgmenthearingscheduled
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcjudgmenthearingscheduled IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N43" s="68" t="inlineStr">
+      <c r="O44" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-14 | 2026-01-18 | 2026-03-27 | 2025-10-15 | 2026-02-04 | 2026-08-21 | 2025-09-16 | 2026-04-13 | 2025-11-29 | 2020-01-22（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="40" customHeight="1" s="74">
-      <c r="A44" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="S44" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_judgement_hearing_set_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_judgement_hearing_set_date`) AS non_null,
+       MIN(`timeline_judgement_hearing_set_date`) AS min_dt, MAX(`timeline_judgement_hearing_set_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T44" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 10/89 · 区间 2023-12-14~2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1" s="74">
+      <c r="A45" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>judgement_entered_date</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcjudgmententered</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>法院正式记录判决的日期（已完成法律事实）；与fcjudgmenthearingscheduled相差约11天属正常——两者测量完全不同时间点，非ETL延迟</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；仅Judicial州</t>
         </is>
       </c>
-      <c r="I44" s="48" t="inlineStr">
+      <c r="I45" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD（Judicial州）</t>
         </is>
       </c>
-      <c r="J44" s="48" t="inlineStr">
+      <c r="J45" s="48" t="inlineStr">
         <is>
           <t>2026-01-07</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="K45" s="12" t="inlineStr">
         <is>
           <t>ETL中间表 port.basic_data_loan_fcl.fcjudgment_end_date（非直接BPS显示字段）</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L45" s="131" t="inlineStr">
+        <is>
+          <t>N/A — BPS timeline_judgement_date 实取 fcjudgmenthearingscheduled，非 fcjudgmententered</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>✅ 7.9% (仅Judicial州)</t>
         </is>
       </c>
-      <c r="M44" s="59" t="inlineStr">
+      <c r="N45" s="126" t="inlineStr">
         <is>
           <t>-- 验证 judgement_entered_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcjudgmententered
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcjudgmententered IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N44" s="68" t="inlineStr">
+      <c r="O45" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-01-10 | 2025-10-20 | 2026-01-07 | 2026-04-08 | 2025-08-25 | 2025-12-29 | 2026-02-04 | 2025-08-13 | 2026-02-13 | 2026-03-20（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="40" customHeight="1" s="74">
-      <c r="A45" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="S45" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS timeline_judgement_date 实取 hearing scheduled，非 fcjudgmententered</t>
+        </is>
+      </c>
+      <c r="T45" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1" s="74">
+      <c r="A46" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>scheduled_sale_date</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcscheduledsaledate</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>止赎拍卖计划日期；任何非空值立即触发最高优先级SALE阶段；随流程推进动态更新</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I45" s="48" t="inlineStr">
+      <c r="I46" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J45" s="48" t="inlineStr">
+      <c r="J46" s="48" t="inlineStr">
         <is>
           <t>2024-05-15</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_sale_date_projected_date / sale_start_date / SALE阶段（最高优先级1）</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L46" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fcscheduledsaledate → timeline_sale_date_set_date / projected）</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>✅ 18.2%</t>
         </is>
       </c>
-      <c r="M45" s="59" t="inlineStr">
+      <c r="N46" s="126" t="inlineStr">
         <is>
           <t>-- 验证 scheduled_sale_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcscheduledsaledate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcscheduledsaledate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N45" s="68" t="inlineStr">
+      <c r="O46" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-06-02 | 2025-09-09 | 2025-05-16 | 2025-08-26 | 2026-06-26 | 2025-06-05 | 2026-07-08 | 2026-06-10 | 2026-06-30 | 2026-07-09（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="40" customHeight="1" s="74">
-      <c r="A46" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="S46" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_sale_date_set_date 取值（date）— 另 timeline_sale_date_projected_date
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_sale_date_set_date`) AS non_null,
+       MIN(`timeline_sale_date_set_date`) AS min_dt, MAX(`timeline_sale_date_set_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T46" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 14/89 · 区间 2025-01-23~2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1" s="74">
+      <c r="A47" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>sale_held_date</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcsalehelddate</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>止赎拍卖实际举行的日期；结合fcresults判断是否为第三方购买</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I46" s="48" t="inlineStr">
+      <c r="I47" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J46" s="48" t="inlineStr">
+      <c r="J47" s="48" t="inlineStr">
         <is>
           <t>2024-05-15</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K47" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_sale_date_held_date / 3rd Party Sale逻辑触发</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="L47" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fcsalehelddate → timeline_sale_date_held_date）</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>✅ 2.1% (仅完成贷款)</t>
         </is>
       </c>
-      <c r="M46" s="59" t="inlineStr">
+      <c r="N47" s="126" t="inlineStr">
         <is>
           <t>-- 验证 sale_held_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcsalehelddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcsalehelddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N46" s="68" t="inlineStr">
+      <c r="O47" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-07 | 2025-12-04 | 2026-05-15 | 2026-05-22 | 2026-05-12 | 2025-10-14 | 2026-03-11 | 2025-11-04 | 2025-12-29（9笔）</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="40" customHeight="1" s="74">
-      <c r="A47" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="S47" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_sale_date_held_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_sale_date_held_date`) AS non_null,
+       MIN(`timeline_sale_date_held_date`) AS min_dt, MAX(`timeline_sale_date_held_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T47" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 11/89 · 区间 2025-01-23~2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1" s="74">
+      <c r="A48" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>deed_recorded_date</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.dtdeedrecorded</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>产权证书登记日期（止赎法律完成标志）；COALESCE第一选项</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I47" s="49" t="inlineStr">
+      <c r="I48" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J47" s="49" t="inlineStr">
+      <c r="J48" s="49" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="K47" s="13" t="inlineStr">
+      <c r="K48" s="13" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_foreclosure_completed_date（COALESCE优先选项）</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L48" s="132" t="inlineStr">
+        <is>
+          <t>COALESCE(dtdeedrecorded, fcremovaldate) → timeline_foreclosure_completed_date</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
         <is>
           <t>✅ ~0% (仅完成贷款)</t>
         </is>
       </c>
-      <c r="M47" s="59" t="inlineStr">
+      <c r="N48" s="126" t="inlineStr">
         <is>
           <t>-- 验证 deed_recorded_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, dtdeedrecorded
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  dtdeedrecorded IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N47" s="68" t="inlineStr">
+      <c r="O48" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-28 | 2026-05-22 | 2025-10-28 | 2025-11-12（4笔）</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="40" customHeight="1" s="74">
-      <c r="A48" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="S48" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_foreclosure_completed_date 取值（date）— COALESCE(dtdeedrecorded,fcremovaldate)
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_foreclosure_completed_date`) AS non_null,
+       MIN(`timeline_foreclosure_completed_date`) AS min_dt, MAX(`timeline_foreclosure_completed_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T48" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 0/89（prod 全空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1" s="74">
+      <c r="A49" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>fcl_removal_date</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcremovaldate</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>FCL流程取消或关闭的日期；COALESCE备用选项</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I48" s="48" t="inlineStr">
+      <c r="I49" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J48" s="48" t="inlineStr">
+      <c r="J49" s="48" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr">
+      <c r="K49" s="12" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_foreclosure_completed_date（COALESCE备用选项）</t>
         </is>
       </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="L49" s="131" t="inlineStr">
+        <is>
+          <t>COALESCE(dtdeedrecorded, fcremovaldate) → timeline_foreclosure_completed_date（与 deed_recorded_date 同列，作回退源）</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>✅ ~2.0% (仅完成贷款)</t>
         </is>
       </c>
-      <c r="M48" s="59" t="inlineStr">
+      <c r="N49" s="126" t="inlineStr">
         <is>
           <t>-- 验证 fcl_removal_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcremovaldate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcremovaldate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N48" s="68" t="inlineStr">
+      <c r="O49" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-02-28 | 2025-11-07 | 2026-05-11 | 2026-05-07 | 2026-05-05 | 2026-03-10 | 2025-11-11 | 2026-03-27 | 2025-08-29 | 2026-04-08（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="40" customHeight="1" s="74">
-      <c r="A49" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="S49" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_foreclosure_completed_date 取值（date）— COALESCE(dtdeedrecorded,fcremovaldate) 的回退源；与 deed_recorded_date 同列
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_foreclosure_completed_date`) AS non_null,
+       MIN(`timeline_foreclosure_completed_date`) AS min_dt, MAX(`timeline_foreclosure_completed_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T49" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 0/89（prod 全空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="74">
+      <c r="A50" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>2.3 FCL时间轴字段 — Time</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>third_party_proceeds_date</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcl3rdpartyproceedsreceiveddate</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>从第三方买家收到拍卖款项的日期</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I49" s="49" t="inlineStr">
+      <c r="I50" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J49" s="49" t="inlineStr">
+      <c r="J50" s="49" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K49" s="13" t="inlineStr">
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>Timeline &gt; timeline_third_party_proceeds_received_date</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="L50" s="132" t="inlineStr">
+        <is>
+          <t>直接取值（fcl3rdpartyproceedsreceiveddate → timeline_third_party_proceeds_received_date）</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
         <is>
           <t>✅ ~0% (极少数完成贷款)</t>
         </is>
       </c>
-      <c r="M49" s="59" t="inlineStr">
+      <c r="N50" s="126" t="inlineStr">
         <is>
           <t>-- 验证 third_party_proceeds_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcl3rdpartyproceedsreceiveddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcl3rdpartyproceedsreceiveddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N49" s="68" t="inlineStr">
+      <c r="O50" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-05-27 | 2026-04-02 | 2026-03-05（3笔）</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" s="74">
-      <c r="A50" s="119" t="inlineStr">
+      <c r="S50" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS timeline_third_party_proceeds_received_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`timeline_third_party_proceeds_received_date`) AS non_null,
+       MIN(`timeline_third_party_proceeds_received_date`) AS min_dt, MAX(`timeline_third_party_proceeds_received_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T50" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 3/89 · 区间 2026-03-05~2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1" s="74">
+      <c r="A51" s="119" t="inlineStr">
         <is>
           <t>Section 2.4 — Hold槽位字段 — Hold历史记录面板（来源：newrez.portnewrezfc，3个槽位×5个字段）</t>
         </is>
       </c>
-      <c r="B50" s="70" t="n"/>
-      <c r="C50" s="70" t="n"/>
-      <c r="D50" s="70" t="n"/>
-      <c r="E50" s="70" t="n"/>
-      <c r="F50" s="70" t="n"/>
-      <c r="G50" s="70" t="n"/>
-      <c r="H50" s="70" t="n"/>
-      <c r="I50" s="70" t="n"/>
-      <c r="J50" s="71" t="n"/>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="3" t="n"/>
-    </row>
-    <row r="51" ht="40" customHeight="1" s="74">
-      <c r="A51" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>2.4 Hold槽位字段 — Hold</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>hold_1_description</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezfc.fchold1description</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>Hold槽1原因文本；自由文本；BPS每次变更追加新行累积完整历史</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>自由文本</t>
-        </is>
-      </c>
-      <c r="I51" s="48" t="inlineStr">
-        <is>
-          <t>BK | LM | Court Delay | Service Delay 等（Newrez扩展枚举可接受）</t>
-        </is>
-      </c>
-      <c r="J51" s="48" t="inlineStr">
-        <is>
-          <t>Loss Mitigation Workout</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>Hold面板 &gt; description列（槽1）</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>✅ 89.6%</t>
-        </is>
-      </c>
-      <c r="M51" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 hold_1_description 取值范围
--- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, fchold1description AS val, COUNT(*) AS cnt
-FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
-  AND  fchold1description IS NOT NULL AND fchold1description != ''
-GROUP  BY dataasof, fchold1description ORDER BY cnt DESC LIMIT 30;</t>
-        </is>
-      </c>
-      <c r="N51" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] Loss Mitigation Workout:21 | Awaiting Funds to Post:16 | Delinquency Review:12 | Bankruptcy Filed:6 | Hearing Set:4 | Court Delay:4 | Client Document Execution:4 | Service Delay:4 | Note Possession Confirmation:3 | Title Resolution:3 | Original Note:2 | Allonge of Note:1 | Service By Publication:1 | Guaranty Agreement:1 | Demand Letter Review:1 | Awaiting Escrow Analysis:1 | Moratorium:1 | Mediation Hearing:1 | FC Payment Research/Dispute:1 | ACT(PA) Letter/Demand Letter/NOI Expiration:1 | Original Assignment:1</t>
-        </is>
-      </c>
+      <c r="B51" s="70" t="n"/>
+      <c r="C51" s="70" t="n"/>
+      <c r="D51" s="70" t="n"/>
+      <c r="E51" s="70" t="n"/>
+      <c r="F51" s="70" t="n"/>
+      <c r="G51" s="70" t="n"/>
+      <c r="H51" s="70" t="n"/>
+      <c r="I51" s="70" t="n"/>
+      <c r="J51" s="71" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="M51" s="3" t="n"/>
     </row>
     <row r="52" ht="40" customHeight="1" s="74">
       <c r="A52" s="12" t="n">
@@ -6965,297 +7876,372 @@
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
+          <t>hold_1_description</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezfc.fchold1description</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Hold槽1原因文本；自由文本；BPS每次变更追加新行累积完整历史</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>自由文本</t>
+        </is>
+      </c>
+      <c r="I52" s="48" t="inlineStr">
+        <is>
+          <t>BK | LM | Court Delay | Service Delay 等（Newrez扩展枚举可接受）</t>
+        </is>
+      </c>
+      <c r="J52" s="48" t="inlineStr">
+        <is>
+          <t>Loss Mitigation Workout</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>Hold面板 &gt; description列（槽1）</t>
+        </is>
+      </c>
+      <c r="L52" s="131" t="inlineStr">
+        <is>
+          <t>3 槽位 UNPIVOT 合并 → description（每槽位追加一行，累积全历史）</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>✅ 89.6%</t>
+        </is>
+      </c>
+      <c r="N52" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 hold_1_description 取值范围
+-- 源表: newrez.portnewrezfc | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, fchold1description AS val, COUNT(*) AS cnt
+FROM   newrez.portnewrezfc
+WHERE  dataasof = '2026-06-01'
+  AND  fchold1description IS NOT NULL AND fchold1description != ''
+GROUP  BY dataasof, fchold1description ORDER BY cnt DESC LIMIT 30;</t>
+        </is>
+      </c>
+      <c r="O52" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] Loss Mitigation Workout:21 | Awaiting Funds to Post:16 | Delinquency Review:12 | Bankruptcy Filed:6 | Hearing Set:4 | Court Delay:4 | Client Document Execution:4 | Service Delay:4 | Note Possession Confirmation:3 | Title Resolution:3 | Original Note:2 | Allonge of Note:1 | Service By Publication:1 | Guaranty Agreement:1 | Demand Letter Review:1 | Awaiting Escrow Analysis:1 | Moratorium:1 | Mediation Hearing:1 | FC Payment Research/Dispute:1 | ACT(PA) Letter/Demand Letter/NOI Expiration:1 | Original Assignment:1</t>
+        </is>
+      </c>
+      <c r="S52" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description 取值（dist）— 3 槽位 UNPIVOT 合并→description
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `description` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_hold
+GROUP  BY `description` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T52" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Loss Mitigation Workout:63 | Service Delay:48 | ∅NULL:44 | Client Document Execution:29 | Court Delay:23 | Awaiting Funds to Post:20 | ACT(PA) Letter/Demand Letter/NOI Expiration:18 | Hearing Set:17 | Mediation Hearing:13 | Delinquency Review:11 | Original Note:10 | Title Resolution:9 | Note Possession Confirmation:8 | Bankruptcy Filed:8 | Copy of Power of Attorney:7 | Copy of Payment History:5 | Original Assignment:5 | Demand Letter Review:4 | Service By Publication:4 | Copy of Periodic Statement:4 | Pending Prior Servicer Doc(s):2 | Awaiting Escrow Analysis:2 | Soldiers and Sailors Relief Act:2 | Allonge of Note:2 | FC Payment Research/Dispute:2 | +15 个取值各1笔:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1" s="74">
+      <c r="A53" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>2.4 Hold槽位字段 — Hold</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
           <t>hold_1_start_date</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold1startdate</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>Hold 1开始日期；同时是BPS提取过滤条件（fchold1startdate IS NOT NULL为入库条件）</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I52" s="48" t="inlineStr">
+      <c r="I53" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J52" s="48" t="inlineStr">
+      <c r="J53" s="48" t="inlineStr">
         <is>
           <t>2024-01-05</t>
         </is>
       </c>
-      <c r="K52" s="12" t="inlineStr">
+      <c r="K53" s="12" t="inlineStr">
         <is>
           <t>Hold面板 &gt; description_start_date（槽1）</t>
         </is>
       </c>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="L53" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fchold1startdate → description_start_date）</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>✅ (与description同步)</t>
         </is>
       </c>
-      <c r="M52" s="59" t="inlineStr">
+      <c r="N53" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_1_start_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold1startdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold1startdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N52" s="68" t="inlineStr">
+      <c r="O53" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-06 | 2026-05-28 | 2026-05-09 | 2026-05-06 | 2026-05-02 | 2026-03-04 | 2026-03-13 | 2026-04-29 | 2025-11-01 | 2026-05-28（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="40" customHeight="1" s="74">
-      <c r="A53" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="S53" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description_start_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`description_start_date`) AS non_null,
+       MIN(`description_start_date`) AS min_dt, MAX(`description_start_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_hold;</t>
+        </is>
+      </c>
+      <c r="T53" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 375/375 · 区间 2019-10-24~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1" s="74">
+      <c r="A54" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>hold_1_end_date</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold1enddate</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>Hold 1结束日期；NULL表示此Hold仍活跃</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；NULL=仍活跃</t>
         </is>
       </c>
-      <c r="I53" s="48" t="inlineStr">
+      <c r="I54" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD（空=Hold仍持续）</t>
         </is>
       </c>
-      <c r="J53" s="48" t="inlineStr">
+      <c r="J54" s="48" t="inlineStr">
         <is>
           <t>2024-03-15</t>
         </is>
       </c>
-      <c r="K53" s="12" t="inlineStr">
+      <c r="K54" s="12" t="inlineStr">
         <is>
           <t>Hold面板 &gt; description_end_date（槽1）</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="L54" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fchold1enddate → description_end_date；NULL=仍生效）</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M53" s="59" t="inlineStr">
+      <c r="N54" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_1_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold1enddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold1enddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N53" s="68" t="inlineStr">
+      <c r="O54" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-07 | 2026-05-11 | 2026-05-07 | 2026-05-05 | 2026-03-10 | 2025-11-11 | 2026-05-21 | 2026-03-27 | 2025-08-22 | 2025-08-14（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="40" customHeight="1" s="74">
-      <c r="A54" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="S54" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description_end_date 取值（date）— NULL=仍生效
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`description_end_date`) AS non_null,
+       MIN(`description_end_date`) AS min_dt, MAX(`description_end_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_hold;</t>
+        </is>
+      </c>
+      <c r="T54" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 357/375 · 区间 2019-11-15~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1" s="74">
+      <c r="A55" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>hold_1_projected_end_date</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold1projectedenddate</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>Hold 1预计结束日期；variance_estimated_hold_days = MAX(槽1/2/3预计结束) − 今日NY</t>
         </is>
       </c>
-      <c r="H54" s="13" t="inlineStr">
+      <c r="H55" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I54" s="49" t="inlineStr">
+      <c r="I55" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J54" s="49" t="inlineStr">
+      <c r="J55" s="49" t="inlineStr">
         <is>
           <t>2024-03-20</t>
         </is>
       </c>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="K55" s="13" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure.variance_estimated_hold_days计算（MAX三槽）</t>
         </is>
       </c>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="L55" s="132" t="inlineStr">
+        <is>
+          <t>N/A — BPS hold 表无 projected end 列</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M54" s="59" t="inlineStr">
+      <c r="N55" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_1_projected_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold1projectedenddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold1projectedenddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N54" s="68" t="inlineStr">
+      <c r="O55" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-01-05 | 2026-07-27 | 2026-07-08 | 2026-07-05 | 2026-07-01 | 2026-05-03 | 2026-06-05 | 2026-06-28 | 2025-11-08 | 2026-06-18（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="40" customHeight="1" s="74">
-      <c r="A55" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>2.4 Hold槽位字段 — Hold</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>hold_2_description</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezfc.fchold2description</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>Hold槽2原因文本（同期存在多个Hold时使用）</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>自由文本</t>
-        </is>
-      </c>
-      <c r="I55" s="48" t="inlineStr">
-        <is>
-          <t>BK | LM | Court Delay | Service Delay 等（Newrez扩展枚举可接受）</t>
-        </is>
-      </c>
-      <c r="J55" s="48" t="inlineStr">
-        <is>
-          <t>Loss Mitigation Workout</t>
-        </is>
-      </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>Hold面板 &gt; description列（槽2）</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>✅ 69.8%</t>
-        </is>
-      </c>
-      <c r="M55" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 hold_2_description 取值范围
--- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, fchold2description AS val, COUNT(*) AS cnt
-FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
-  AND  fchold2description IS NOT NULL AND fchold2description != ''
-GROUP  BY dataasof, fchold2description ORDER BY cnt DESC LIMIT 30;</t>
-        </is>
-      </c>
-      <c r="N55" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] Loss Mitigation Workout:16 | Client Document Execution:9 | Court Delay:8 | ACT(PA) Letter/Demand Letter/NOI Expiration:7 | Awaiting Funds to Post:6 | Delinquency Review:5 | Service Delay:4 | Hearing Set:4 | Bankruptcy Filed:3 | Original Note:2 | Title Resolution:2 | Copy of Payment History:2 | Note Possession Confirmation:1 | Copy of Periodic Statement:1 | Mediation Hearing:1 | Allonge of Note:1 | FC Escrow/Corp Breakdown Needed:1 | HAF - Homeowner Assistance Fund:1</t>
+      <c r="S55" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS hold 表无 projected end 列</t>
+        </is>
+      </c>
+      <c r="T55" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -7270,297 +8256,372 @@
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
+          <t>hold_2_description</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezfc.fchold2description</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Hold槽2原因文本（同期存在多个Hold时使用）</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>自由文本</t>
+        </is>
+      </c>
+      <c r="I56" s="48" t="inlineStr">
+        <is>
+          <t>BK | LM | Court Delay | Service Delay 等（Newrez扩展枚举可接受）</t>
+        </is>
+      </c>
+      <c r="J56" s="48" t="inlineStr">
+        <is>
+          <t>Loss Mitigation Workout</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Hold面板 &gt; description列（槽2）</t>
+        </is>
+      </c>
+      <c r="L56" s="131" t="inlineStr">
+        <is>
+          <t>3 槽位 UNPIVOT 合并 → description（同 hold_1）</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>✅ 69.8%</t>
+        </is>
+      </c>
+      <c r="N56" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 hold_2_description 取值范围
+-- 源表: newrez.portnewrezfc | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, fchold2description AS val, COUNT(*) AS cnt
+FROM   newrez.portnewrezfc
+WHERE  dataasof = '2026-06-01'
+  AND  fchold2description IS NOT NULL AND fchold2description != ''
+GROUP  BY dataasof, fchold2description ORDER BY cnt DESC LIMIT 30;</t>
+        </is>
+      </c>
+      <c r="O56" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] Loss Mitigation Workout:16 | Client Document Execution:9 | Court Delay:8 | ACT(PA) Letter/Demand Letter/NOI Expiration:7 | Awaiting Funds to Post:6 | Delinquency Review:5 | Service Delay:4 | Hearing Set:4 | Bankruptcy Filed:3 | Original Note:2 | Title Resolution:2 | Copy of Payment History:2 | Note Possession Confirmation:1 | Copy of Periodic Statement:1 | Mediation Hearing:1 | Allonge of Note:1 | FC Escrow/Corp Breakdown Needed:1 | HAF - Homeowner Assistance Fund:1</t>
+        </is>
+      </c>
+      <c r="S56" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description 取值（dist）— 同 hold_1（合并入 description）
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `description` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_hold
+GROUP  BY `description` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T56" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Loss Mitigation Workout:63 | Service Delay:48 | ∅NULL:44 | Client Document Execution:29 | Court Delay:23 | Awaiting Funds to Post:20 | ACT(PA) Letter/Demand Letter/NOI Expiration:18 | Hearing Set:17 | Mediation Hearing:13 | Delinquency Review:11 | Original Note:10 | Title Resolution:9 | Note Possession Confirmation:8 | Bankruptcy Filed:8 | Copy of Power of Attorney:7 | Copy of Payment History:5 | Original Assignment:5 | Demand Letter Review:4 | Service By Publication:4 | Copy of Periodic Statement:4 | Pending Prior Servicer Doc(s):2 | Awaiting Escrow Analysis:2 | Soldiers and Sailors Relief Act:2 | Allonge of Note:2 | FC Payment Research/Dispute:2 | +15 个取值各1笔:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1" s="74">
+      <c r="A57" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>2.4 Hold槽位字段 — Hold</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
           <t>hold_2_start_date</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold2startdate</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Hold 2开始日期</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I56" s="48" t="inlineStr">
+      <c r="I57" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J56" s="48" t="inlineStr">
+      <c r="J57" s="48" t="inlineStr">
         <is>
           <t>2024-01-05</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
+      <c r="K57" s="12" t="inlineStr">
         <is>
           <t>Hold面板 &gt; description_start_date（槽2）</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="L57" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fchold2startdate → description_start_date）</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M56" s="59" t="inlineStr">
+      <c r="N57" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_2_start_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold2startdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold2startdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N56" s="68" t="inlineStr">
+      <c r="O57" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-06 | 2026-05-28 | 2026-05-09 | 2026-05-06 | 2026-05-02 | 2026-03-04 | 2026-03-13 | 2026-04-28 | 2025-10-24 | 2026-05-04（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="40" customHeight="1" s="74">
-      <c r="A57" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="S57" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description_start_date 取值（date）— 同 hold_1
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`description_start_date`) AS non_null,
+       MIN(`description_start_date`) AS min_dt, MAX(`description_start_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_hold;</t>
+        </is>
+      </c>
+      <c r="T57" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 375/375 · 区间 2019-10-24~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1" s="74">
+      <c r="A58" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>hold_2_end_date</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold2enddate</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>Hold 2结束日期；NULL=仍活跃</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；NULL=仍活跃</t>
         </is>
       </c>
-      <c r="I57" s="48" t="inlineStr">
+      <c r="I58" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD（空=Hold仍持续）</t>
         </is>
       </c>
-      <c r="J57" s="48" t="inlineStr">
+      <c r="J58" s="48" t="inlineStr">
         <is>
           <t>2024-03-15</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
+      <c r="K58" s="12" t="inlineStr">
         <is>
           <t>Hold面板 &gt; description_end_date（槽2）</t>
         </is>
       </c>
-      <c r="L57" s="7" t="inlineStr">
+      <c r="L58" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fchold2enddate → description_end_date）</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M57" s="59" t="inlineStr">
+      <c r="N58" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_2_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold2enddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold2enddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N57" s="68" t="inlineStr">
+      <c r="O58" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-07 | 2026-05-11 | 2026-05-07 | 2026-05-05 | 2026-03-10 | 2026-05-08 | 2026-04-29 | 2025-10-30 | 2026-05-05 | 2026-05-21（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="40" customHeight="1" s="74">
-      <c r="A58" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="S58" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description_end_date 取值（date）— 同 hold_1
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`description_end_date`) AS non_null,
+       MIN(`description_end_date`) AS min_dt, MAX(`description_end_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_hold;</t>
+        </is>
+      </c>
+      <c r="T58" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 357/375 · 区间 2019-11-15~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1" s="74">
+      <c r="A59" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>hold_2_projected_end_date</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold2projectedenddate</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
+      <c r="F59" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>Hold 2预计结束日期；参与MAX计算</t>
         </is>
       </c>
-      <c r="H58" s="13" t="inlineStr">
+      <c r="H59" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I58" s="49" t="inlineStr">
+      <c r="I59" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J58" s="49" t="inlineStr">
+      <c r="J59" s="49" t="inlineStr">
         <is>
           <t>2024-03-20</t>
         </is>
       </c>
-      <c r="K58" s="13" t="inlineStr">
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>variance_estimated_hold_days计算（与槽1/3并列）</t>
         </is>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="L59" s="132" t="inlineStr">
+        <is>
+          <t>N/A — BPS hold 表无 projected end 列</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M58" s="59" t="inlineStr">
+      <c r="N59" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_2_projected_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold2projectedenddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold2projectedenddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N58" s="68" t="inlineStr">
+      <c r="O59" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-01-05 | 2026-07-27 | 2026-07-08 | 2026-07-05 | 2026-07-01 | 2026-05-03 | 2026-05-08 | 2026-05-28 | 2025-10-30 | 2026-06-03（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="40" customHeight="1" s="74">
-      <c r="A59" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>2.4 Hold槽位字段 — Hold</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>hold_3_description</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezfc.fchold3description</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>Hold槽3原因文本（第三个并行Hold）</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>自由文本</t>
-        </is>
-      </c>
-      <c r="I59" s="48" t="inlineStr">
-        <is>
-          <t>BK | LM | Court Delay | Service Delay 等（Newrez扩展枚举可接受）</t>
-        </is>
-      </c>
-      <c r="J59" s="48" t="inlineStr">
-        <is>
-          <t>Loss Mitigation Workout</t>
-        </is>
-      </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>Hold面板 &gt; description列（槽3）</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>✅ 52.6%</t>
-        </is>
-      </c>
-      <c r="M59" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 hold_3_description 取值范围
--- 源表: newrez.portnewrezfc | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, fchold3description AS val, COUNT(*) AS cnt
-FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
-  AND  fchold3description IS NOT NULL AND fchold3description != ''
-GROUP  BY dataasof, fchold3description ORDER BY cnt DESC LIMIT 30;</t>
-        </is>
-      </c>
-      <c r="N59" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] Client Document Execution:8 | Loss Mitigation Workout:6 | Court Delay:5 | Mediation Hearing:3 | Original Note:3 | Hearing Set:3 | Service Delay:3 | Allonge of Note:2 | Note Possession Confirmation:2 | Bankruptcy Filed:2 | Title Resolution:2 | ACT(PA) Letter/Demand Letter/NOI Expiration:2 | Service By Publication:2 | Copy of Payment History:1 | Awaiting Escrow Analysis:1 | Delinquency Review:1 | Copy of Note:1 | FC Payment Research/Dispute:1 | MERS Assignment Needed:1 | Guaranty Agreement:1 | Awaiting Funds to Post:1 | FEMA Hold:1 | Copy of Power of Attorney:1 | COVID Affected:1 | Court Delay Mid Term (46 - 90 Days):1</t>
+      <c r="S59" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS hold 表无 projected end 列</t>
+        </is>
+      </c>
+      <c r="T59" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -7575,865 +8636,1060 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
+          <t>hold_3_description</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezfc.fchold3description</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Hold槽3原因文本（第三个并行Hold）</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>自由文本</t>
+        </is>
+      </c>
+      <c r="I60" s="48" t="inlineStr">
+        <is>
+          <t>BK | LM | Court Delay | Service Delay 等（Newrez扩展枚举可接受）</t>
+        </is>
+      </c>
+      <c r="J60" s="48" t="inlineStr">
+        <is>
+          <t>Loss Mitigation Workout</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>Hold面板 &gt; description列（槽3）</t>
+        </is>
+      </c>
+      <c r="L60" s="131" t="inlineStr">
+        <is>
+          <t>3 槽位 UNPIVOT 合并 → description（同 hold_1）</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>✅ 52.6%</t>
+        </is>
+      </c>
+      <c r="N60" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 hold_3_description 取值范围
+-- 源表: newrez.portnewrezfc | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, fchold3description AS val, COUNT(*) AS cnt
+FROM   newrez.portnewrezfc
+WHERE  dataasof = '2026-06-01'
+  AND  fchold3description IS NOT NULL AND fchold3description != ''
+GROUP  BY dataasof, fchold3description ORDER BY cnt DESC LIMIT 30;</t>
+        </is>
+      </c>
+      <c r="O60" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] Client Document Execution:8 | Loss Mitigation Workout:6 | Court Delay:5 | Mediation Hearing:3 | Original Note:3 | Hearing Set:3 | Service Delay:3 | Allonge of Note:2 | Note Possession Confirmation:2 | Bankruptcy Filed:2 | Title Resolution:2 | ACT(PA) Letter/Demand Letter/NOI Expiration:2 | Service By Publication:2 | Copy of Payment History:1 | Awaiting Escrow Analysis:1 | Delinquency Review:1 | Copy of Note:1 | FC Payment Research/Dispute:1 | MERS Assignment Needed:1 | Guaranty Agreement:1 | Awaiting Funds to Post:1 | FEMA Hold:1 | Copy of Power of Attorney:1 | COVID Affected:1 | Court Delay Mid Term (46 - 90 Days):1</t>
+        </is>
+      </c>
+      <c r="S60" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description 取值（dist）— 同 hold_1（合并入 description）
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `description` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_hold
+GROUP  BY `description` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T60" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Loss Mitigation Workout:63 | Service Delay:48 | ∅NULL:44 | Client Document Execution:29 | Court Delay:23 | Awaiting Funds to Post:20 | ACT(PA) Letter/Demand Letter/NOI Expiration:18 | Hearing Set:17 | Mediation Hearing:13 | Delinquency Review:11 | Original Note:10 | Title Resolution:9 | Note Possession Confirmation:8 | Bankruptcy Filed:8 | Copy of Power of Attorney:7 | Copy of Payment History:5 | Original Assignment:5 | Demand Letter Review:4 | Service By Publication:4 | Copy of Periodic Statement:4 | Pending Prior Servicer Doc(s):2 | Awaiting Escrow Analysis:2 | Soldiers and Sailors Relief Act:2 | Allonge of Note:2 | FC Payment Research/Dispute:2 | +15 个取值各1笔:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1" s="74">
+      <c r="A61" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>2.4 Hold槽位字段 — Hold</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
           <t>hold_3_start_date</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold3startdate</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>Hold 3开始日期</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I60" s="48" t="inlineStr">
+      <c r="I61" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J60" s="48" t="inlineStr">
+      <c r="J61" s="48" t="inlineStr">
         <is>
           <t>2024-01-05</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr">
+      <c r="K61" s="12" t="inlineStr">
         <is>
           <t>Hold面板 &gt; description_start_date（槽3）</t>
         </is>
       </c>
-      <c r="L60" s="7" t="inlineStr">
+      <c r="L61" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fchold3startdate → description_start_date）</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M60" s="59" t="inlineStr">
+      <c r="N61" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_3_start_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold3startdate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold3startdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N60" s="68" t="inlineStr">
+      <c r="O61" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-05-26 | 2026-04-24 | 2026-02-03 | 2026-04-27 | 2026-02-20 | 2026-01-21 | 2026-04-27 | 2025-10-06 | 2026-03-27 | 2026-02-18（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="40" customHeight="1" s="74">
-      <c r="A61" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="S61" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description_start_date 取值（date）— 同 hold_1
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`description_start_date`) AS non_null,
+       MIN(`description_start_date`) AS min_dt, MAX(`description_start_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_hold;</t>
+        </is>
+      </c>
+      <c r="T61" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 375/375 · 区间 2019-10-24~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1" s="74">
+      <c r="A62" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>hold_3_end_date</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold3enddate</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>Hold 3结束日期；NULL=仍活跃</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；NULL=仍活跃</t>
         </is>
       </c>
-      <c r="I61" s="48" t="inlineStr">
+      <c r="I62" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD（空=Hold仍持续）</t>
         </is>
       </c>
-      <c r="J61" s="48" t="inlineStr">
+      <c r="J62" s="48" t="inlineStr">
         <is>
           <t>2024-03-15</t>
         </is>
       </c>
-      <c r="K61" s="12" t="inlineStr">
+      <c r="K62" s="12" t="inlineStr">
         <is>
           <t>Hold面板 &gt; description_end_date（槽3）</t>
         </is>
       </c>
-      <c r="L61" s="7" t="inlineStr">
+      <c r="L62" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fchold3enddate → description_end_date）</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M61" s="59" t="inlineStr">
+      <c r="N62" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_3_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold3enddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold3enddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N61" s="68" t="inlineStr">
+      <c r="O62" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-27 | 2026-04-22 | 2026-04-30 | 2026-02-24 | 2026-04-09 | 2026-04-27 | 2025-10-23 | 2026-04-14 | 2026-03-27 | 2025-12-26（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="40" customHeight="1" s="74">
-      <c r="A62" s="13" t="n">
-        <v>56</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="S62" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS description_end_date 取值（date）— 同 hold_1
+-- 表: bpms.sync_loan_foreclosure_hold | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`description_end_date`) AS non_null,
+       MIN(`description_end_date`) AS min_dt, MAX(`description_end_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_hold;</t>
+        </is>
+      </c>
+      <c r="T62" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 357/375 · 区间 2019-11-15~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1" s="74">
+      <c r="A63" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>hold_3_projected_end_date</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold3projectedenddate</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G62" s="13" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>Hold 3预计结束日期；参与MAX计算</t>
         </is>
       </c>
-      <c r="H62" s="13" t="inlineStr">
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I62" s="49" t="inlineStr">
+      <c r="I63" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J62" s="49" t="inlineStr">
+      <c r="J63" s="49" t="inlineStr">
         <is>
           <t>2024-03-20</t>
         </is>
       </c>
-      <c r="K62" s="13" t="inlineStr">
+      <c r="K63" s="13" t="inlineStr">
         <is>
           <t>variance_estimated_hold_days计算（与槽1/2并列）</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr">
+      <c r="L63" s="132" t="inlineStr">
+        <is>
+          <t>N/A — BPS hold 表无 projected end 列</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M62" s="59" t="inlineStr">
+      <c r="N63" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_3_projected_end_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold3projectedenddate
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold3projectedenddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N62" s="68" t="inlineStr">
+      <c r="O63" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-07-26 | 2026-05-01 | 2026-05-16 | 2026-04-30 | 2026-04-13 | 2026-04-13 | 2026-05-27 | 2025-10-31 | 2026-05-26 | 2026-04-19（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="40" customHeight="1" s="74">
-      <c r="A63" s="13" t="n">
-        <v>57</v>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="S63" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS hold 表无 projected end 列</t>
+        </is>
+      </c>
+      <c r="T63" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1" s="74">
+      <c r="A64" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>hold_1_modified_date</t>
         </is>
       </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.holdmodified</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>Hold槽1最后修改日</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I63" s="49" t="inlineStr">
+      <c r="I64" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J63" s="49" t="inlineStr">
+      <c r="J64" s="49" t="inlineStr">
         <is>
           <t>2024-02-20</t>
         </is>
       </c>
-      <c r="K63" s="13" t="inlineStr">
+      <c r="K64" s="13" t="inlineStr">
         <is>
           <t>Hold槽1修改日追踪</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr">
+      <c r="L64" s="132" t="inlineStr">
+        <is>
+          <t>N/A — BPS hold 表无 modified 列</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>✅ 82.1%</t>
         </is>
       </c>
-      <c r="M63" s="59" t="inlineStr">
+      <c r="N64" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_1_modified_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, holdmodified
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  holdmodified IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N63" s="68" t="inlineStr">
+      <c r="O64" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-07 | 2026-05-28 | 2026-05-11 | 2026-05-07 | 2026-05-05 | 2026-03-10 | 2026-05-12 | 2026-04-29 | 2025-11-11 | 2026-05-29（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="40" customHeight="1" s="74">
-      <c r="A64" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="S64" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS hold 表无 modified 列</t>
+        </is>
+      </c>
+      <c r="T64" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1" s="74">
+      <c r="A65" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>hold_2_modified_date</t>
         </is>
       </c>
-      <c r="D64" s="20" t="inlineStr">
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.holdmodified2</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>Hold槽2最后修改日</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
+      <c r="H65" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I64" s="49" t="inlineStr">
+      <c r="I65" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J64" s="49" t="inlineStr">
+      <c r="J65" s="49" t="inlineStr">
         <is>
           <t>2024-02-20</t>
         </is>
       </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="K65" s="13" t="inlineStr">
         <is>
           <t>Hold槽2修改日追踪</t>
         </is>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="L65" s="132" t="inlineStr">
+        <is>
+          <t>N/A — BPS hold 表无 modified 列</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>✅ 82.1%</t>
         </is>
       </c>
-      <c r="M64" s="59" t="inlineStr">
+      <c r="N65" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_2_modified_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, holdmodified2
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  holdmodified2 IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N64" s="68" t="inlineStr">
+      <c r="O65" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-07 | 2026-05-28 | 2026-05-11 | 2026-05-07 | 2026-05-05 | 2026-03-10 | 2026-05-08 | 2026-04-29 | 2025-10-30 | 2026-05-05（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="40" customHeight="1" s="74">
-      <c r="A65" s="13" t="n">
-        <v>59</v>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="S65" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS hold 表无 modified 列</t>
+        </is>
+      </c>
+      <c r="T65" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" s="74">
+      <c r="A66" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>2.4 Hold槽位字段 — Hold</t>
         </is>
       </c>
-      <c r="C65" s="19" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>hold_3_modified_date</t>
         </is>
       </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.holdmodified3</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>Hold槽3最后修改日</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I65" s="49" t="inlineStr">
+      <c r="I66" s="49" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J65" s="49" t="inlineStr">
+      <c r="J66" s="49" t="inlineStr">
         <is>
           <t>2024-02-20</t>
         </is>
       </c>
-      <c r="K65" s="13" t="inlineStr">
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>Hold槽3修改日追踪</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
+      <c r="L66" s="132" t="inlineStr">
+        <is>
+          <t>N/A — BPS hold 表无 modified 列</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
         <is>
           <t>✅ 82.1%</t>
         </is>
       </c>
-      <c r="M65" s="59" t="inlineStr">
+      <c r="N66" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_3_modified_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, holdmodified3
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  holdmodified3 IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N65" s="68" t="inlineStr">
+      <c r="O66" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-05-27 | 2026-04-27 | 2026-04-22 | 2026-04-27 | 2026-02-26 | 2026-04-09 | 2026-04-27 | 2025-10-23 | 2026-04-14 | 2026-03-27（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="18" customHeight="1" s="74">
-      <c r="A66" s="119" t="inlineStr">
+      <c r="S66" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS hold 表无 modified 列</t>
+        </is>
+      </c>
+      <c r="T66" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1" s="74">
+      <c r="A67" s="119" t="inlineStr">
         <is>
           <t>Section 2.5 — 竞标与销售字段 — Bid Approval面板</t>
         </is>
       </c>
-      <c r="B66" s="70" t="n"/>
-      <c r="C66" s="70" t="n"/>
-      <c r="D66" s="70" t="n"/>
-      <c r="E66" s="70" t="n"/>
-      <c r="F66" s="70" t="n"/>
-      <c r="G66" s="70" t="n"/>
-      <c r="H66" s="70" t="n"/>
-      <c r="I66" s="70" t="n"/>
-      <c r="J66" s="71" t="n"/>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="3" t="n"/>
-    </row>
-    <row r="67" ht="40" customHeight="1" s="74">
-      <c r="A67" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="70" t="n"/>
+      <c r="C67" s="70" t="n"/>
+      <c r="D67" s="70" t="n"/>
+      <c r="E67" s="70" t="n"/>
+      <c r="F67" s="70" t="n"/>
+      <c r="G67" s="70" t="n"/>
+      <c r="H67" s="70" t="n"/>
+      <c r="I67" s="70" t="n"/>
+      <c r="J67" s="71" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="M67" s="3" t="n"/>
+    </row>
+    <row r="68" ht="40" customHeight="1" s="74">
+      <c r="A68" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>2.5 竞标与销售字段 — Bid A</t>
         </is>
       </c>
-      <c r="C67" s="19" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>bid_amount</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcbidamount</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>Servicer报告的止赎竞标金额；仅拍卖临近时填充（active FCL约9%填充率）</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="H68" s="13" t="inlineStr">
         <is>
           <t>金额（小数）</t>
         </is>
       </c>
-      <c r="I67" s="49" t="inlineStr">
+      <c r="I68" s="49" t="inlineStr">
         <is>
           <t>正数，单位 USD</t>
         </is>
       </c>
-      <c r="J67" s="49" t="inlineStr">
+      <c r="J68" s="49" t="inlineStr">
         <is>
           <t>160000.00</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K68" s="13" t="inlineStr">
         <is>
           <t>Bid Approval &gt; bid_approval_bid_amount / FCL Summary &gt; summary_foreclosure_bid_amount</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="L68" s="132" t="inlineStr">
+        <is>
+          <t>直接取值（fcbidamount → summary_foreclosure_bid_amount / summary_srv_fc_bid_amount）</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
         <is>
           <t>✅ 9.0%（fcbidamount，$90,000~$543,305.96）</t>
         </is>
       </c>
-      <c r="M67" s="59" t="inlineStr">
+      <c r="N68" s="126" t="inlineStr">
         <is>
           <t>-- 验证 bid_amount 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcbidamount
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcbidamount IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N67" s="68" t="inlineStr">
+      <c r="O68" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 288000.0000000000000000 | 154591.0100000000000000 | 136392.4400000000000000 | 164738.0000000000000000 | 250540.4900000000000000 | 355000.0000000000000000 | 301500.0000000000000000 | 260555.0000000000000000 | 390832.5000000000000000 | 125366.7300000000000000（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="40" customHeight="1" s="74">
-      <c r="A68" s="13" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="S68" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_foreclosure_bid_amount 取值（numeric）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`summary_foreclosure_bid_amount`) AS non_null,
+       MIN(`summary_foreclosure_bid_amount`) AS min_v, MAX(`summary_foreclosure_bid_amount`) AS max_v, ROUND(AVG(`summary_foreclosure_bid_amount`),2) AS avg_v
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T68" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 16/89 · 区间 90000~543305.96 · 均值 265705.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1" s="74">
+      <c r="A69" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>2.5 竞标与销售字段 — Bid A</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>approved_bid_price</t>
         </is>
       </c>
-      <c r="D68" s="20" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcapprbidprice</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>BPS内部竞标审批流程后的已批准竞标金额；可能与fcbidamount不同</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
+      <c r="H69" s="13" t="inlineStr">
         <is>
           <t>金额（小数）</t>
         </is>
       </c>
-      <c r="I68" s="49" t="inlineStr">
+      <c r="I69" s="49" t="inlineStr">
         <is>
           <t>正数，单位 USD</t>
         </is>
       </c>
-      <c r="J68" s="49" t="inlineStr">
+      <c r="J69" s="49" t="inlineStr">
         <is>
           <t>162000.00</t>
         </is>
       </c>
-      <c r="K68" s="13" t="inlineStr">
+      <c r="K69" s="13" t="inlineStr">
         <is>
           <t>Bid Approval &gt; bid_approval_bid_amount（审批视角）</t>
         </is>
       </c>
-      <c r="L68" s="7" t="inlineStr">
+      <c r="L69" s="132" t="inlineStr">
+        <is>
+          <t>直接取值（fcapprbidprice → bid_approval_bid_amount；Bid Approval 面板）</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
         <is>
           <t>✅ 8.9%（fcapprbidprice，$90,000~$536,008.42）</t>
         </is>
       </c>
-      <c r="M68" s="59" t="inlineStr">
+      <c r="N69" s="126" t="inlineStr">
         <is>
           <t>-- 验证 approved_bid_price 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcapprbidprice
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcapprbidprice IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N68" s="68" t="inlineStr">
+      <c r="O69" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 288000.0000000000000000 | 136392.4400000000000000 | 164738.0000000000000000 | 250540.4900000000000000 | 355000.0000000000000000 | 301500.0000000000000000 | 260555.0000000000000000 | 390832.5000000000000000 | 123294.5700000000000000 | 230805.9400000000000000（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="40" customHeight="1" s="74">
-      <c r="A69" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="S69" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS bid_approval_bid_amount 取值（numeric）— Bid Approval 面板
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`bid_approval_bid_amount`) AS non_null,
+       MIN(`bid_approval_bid_amount`) AS min_v, MAX(`bid_approval_bid_amount`) AS max_v, ROUND(AVG(`bid_approval_bid_amount`),2) AS avg_v
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T69" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 16/89 · 区间 90000~543305.96 · 均值 265705.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1" s="74">
+      <c r="A70" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>2.5 竞标与销售字段 — Bid A</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>sale_amount</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fcsaleamount</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G69" s="12" t="inlineStr">
+      <c r="G70" s="12" t="inlineStr">
         <is>
           <t>止赎拍卖实际成交金额；填充率(4.7%)高于fcsalehelddate(2.1%)，疑似字段顺序问题（见doc 13 Q9）</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr">
+      <c r="H70" s="12" t="inlineStr">
         <is>
           <t>金额（小数）</t>
         </is>
       </c>
-      <c r="I69" s="48" t="inlineStr">
+      <c r="I70" s="48" t="inlineStr">
         <is>
           <t>正数，单位 USD</t>
         </is>
       </c>
-      <c r="J69" s="48" t="inlineStr">
+      <c r="J70" s="48" t="inlineStr">
         <is>
           <t>170000.00</t>
         </is>
       </c>
-      <c r="K69" s="12" t="inlineStr">
+      <c r="K70" s="12" t="inlineStr">
         <is>
           <t>FCL Summary &gt; summary_foreclosure_sale_amount</t>
         </is>
       </c>
-      <c r="L69" s="8" t="inlineStr">
+      <c r="L70" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（fcsaleamount → summary_foreclosure_sale_amount）</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
         <is>
           <t>⚠️ 4.7%（fcsaleamount，$90,001~$400,000；填充率异常，见doc 13 Q9）</t>
         </is>
       </c>
-      <c r="M69" s="61" t="inlineStr">
+      <c r="N70" s="128" t="inlineStr">
         <is>
           <t>-- 验证 sale_amount 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fcsaleamount
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fcsaleamount IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N69" s="68" t="inlineStr">
+      <c r="O70" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 288000.0000000000000000 | 165900.0000000000000000 | 164738.0000000000000000 | 200100.0000000000000000 | 260555.0000000000000000 | 357200.0000000000000000 | 203122.0000000000000000 | 274000.0000000000000000 | 400000.0000000000000000 | 90001.0000000000000000（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="18" customHeight="1" s="74">
-      <c r="A70" s="119" t="inlineStr">
+      <c r="S70" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS summary_foreclosure_sale_amount 取值（numeric）
+-- 表: bpms.sync_loan_foreclosure | 运行于: mysql_prod（只读）
+-- as-of: 主表无 dataasof/fctrdt（upsert，update_time 实测全 NULL）；ETL 载入≈2026-06-03（取自 sync_fcl_stage_info.update_time）
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`summary_foreclosure_sale_amount`) AS non_null,
+       MIN(`summary_foreclosure_sale_amount`) AS min_v, MAX(`summary_foreclosure_sale_amount`) AS max_v, ROUND(AVG(`summary_foreclosure_sale_amount`),2) AS avg_v
+FROM   bpms.sync_loan_foreclosure;</t>
+        </is>
+      </c>
+      <c r="T70" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 2026-06-01(主表无嵌入,同 ETL 周期 Newrez 源日)·ETL载入 2026-06-03] 非空 10/89 · 区间 90001~400000 · 均值 240361.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1" s="74">
+      <c r="A71" s="119" t="inlineStr">
         <is>
           <t>Section 2.6 — 贷款属性与风险增强字段 — Newrez已提供但系统尚未使用</t>
         </is>
       </c>
-      <c r="B70" s="70" t="n"/>
-      <c r="C70" s="70" t="n"/>
-      <c r="D70" s="70" t="n"/>
-      <c r="E70" s="70" t="n"/>
-      <c r="F70" s="70" t="n"/>
-      <c r="G70" s="70" t="n"/>
-      <c r="H70" s="70" t="n"/>
-      <c r="I70" s="70" t="n"/>
-      <c r="J70" s="71" t="n"/>
-      <c r="K70" s="2" t="n"/>
-      <c r="L70" s="3" t="n"/>
-    </row>
-    <row r="71" ht="40" customHeight="1" s="74">
-      <c r="A71" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="70" t="n"/>
+      <c r="C71" s="70" t="n"/>
+      <c r="D71" s="70" t="n"/>
+      <c r="E71" s="70" t="n"/>
+      <c r="F71" s="70" t="n"/>
+      <c r="G71" s="70" t="n"/>
+      <c r="H71" s="70" t="n"/>
+      <c r="I71" s="70" t="n"/>
+      <c r="J71" s="71" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="M71" s="3" t="n"/>
+    </row>
+    <row r="72" ht="40" customHeight="1" s="74">
+      <c r="A72" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>2.6 贷款属性与风险增强字段 — N</t>
         </is>
       </c>
-      <c r="C71" s="16" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>investor_loan_id</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.investorloanid</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G71" s="12" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>投资人（如房利美/房地美/私募基金）视角的贷款号；不同于系统loan_id和servicer_loan_id；用于投资人报告对账</t>
         </is>
       </c>
-      <c r="H71" s="12" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
         <is>
           <t>投资人贷款号字符串</t>
         </is>
       </c>
-      <c r="I71" s="48" t="inlineStr">
+      <c r="I72" s="48" t="inlineStr">
         <is>
           <t>投资人贷款编号</t>
         </is>
       </c>
-      <c r="J71" s="48" t="inlineStr">
+      <c r="J72" s="48" t="inlineStr">
         <is>
           <t>INV-20240110-088</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr">
+      <c r="K72" s="12" t="inlineStr">
         <is>
           <t>投资人报告对账 / 跨Servicer转让追踪（当前ETL未使用）</t>
         </is>
       </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="L72" s="131" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>✅ 100%</t>
         </is>
       </c>
-      <c r="M71" s="59" t="inlineStr">
+      <c r="N72" s="126" t="inlineStr">
         <is>
           <t>-- 验证 investor_loan_id 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, investorloanid
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  investorloanid IS NOT NULL AND investorloanid != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N71" s="68" t="inlineStr">
+      <c r="O72" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 5087355 | 5084227 | 5085432 | 5085637 | 5084093 | 5085003 | 8195317 | 5086934 | 5084351 | 5085356（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="40" customHeight="1" s="74">
-      <c r="A72" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>2.6 贷款属性与风险增强字段 — N</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>lien_position</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezgeneral.lienposition（另 portnewrezfc.jr_sr_lien_flag 为顺位标志）</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>留置权优先级：1=第一顺位（高级）；2=第二顺位（次级）；次级贷款止赎必须考虑第一顺位优先索偿权，FCL策略根本不同</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="inlineStr">
-        <is>
-          <t>1=第一顺位(Senior) / 2=第二顺位(Junior)</t>
-        </is>
-      </c>
-      <c r="I72" s="48" t="inlineStr">
-        <is>
-          <t>1（First Lien）/ 2（Second Lien）</t>
-        </is>
-      </c>
-      <c r="J72" s="48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" s="12" t="inlineStr">
-        <is>
-          <t>留置权风险分析 / Junior Lien FCL策略差异化（当前ETL未使用）</t>
-        </is>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>✅ 100%（lienposition，1或2，portnewrezgeneral实测）</t>
-        </is>
-      </c>
-      <c r="M72" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 lien_position 取值范围
--- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, lienposition AS val, COUNT(*) AS cnt
-FROM   newrez.portnewrezgeneral
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezgeneral)
-  AND  lienposition IS NOT NULL AND lienposition != ''
-GROUP  BY dataasof, lienposition ORDER BY cnt DESC LIMIT 30;</t>
-        </is>
-      </c>
-      <c r="N72" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] 1:5025 | 2:27</t>
+      <c r="S72" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T72" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -8448,144 +9704,175 @@
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
+          <t>lien_position</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezgeneral.lienposition（另 portnewrezfc.jr_sr_lien_flag 为顺位标志）</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>留置权优先级：1=第一顺位（高级）；2=第二顺位（次级）；次级贷款止赎必须考虑第一顺位优先索偿权，FCL策略根本不同</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>1=第一顺位(Senior) / 2=第二顺位(Junior)</t>
+        </is>
+      </c>
+      <c r="I73" s="48" t="inlineStr">
+        <is>
+          <t>1（First Lien）/ 2（Second Lien）</t>
+        </is>
+      </c>
+      <c r="J73" s="48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>留置权风险分析 / Junior Lien FCL策略差异化（当前ETL未使用）</t>
+        </is>
+      </c>
+      <c r="L73" s="131" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>✅ 100%（lienposition，1或2，portnewrezgeneral实测）</t>
+        </is>
+      </c>
+      <c r="N73" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 lien_position 取值范围
+-- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, lienposition AS val, COUNT(*) AS cnt
+FROM   newrez.portnewrezgeneral
+WHERE  dataasof = '2026-06-01'
+  AND  lienposition IS NOT NULL AND lienposition != ''
+GROUP  BY dataasof, lienposition ORDER BY cnt DESC LIMIT 30;</t>
+        </is>
+      </c>
+      <c r="O73" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] 1:5025 | 2:27</t>
+        </is>
+      </c>
+      <c r="S73" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T73" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1" s="74">
+      <c r="A74" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>2.6 贷款属性与风险增强字段 — N</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
           <t>interest_paid_through_date</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezgeneral.interestpaidthroughdate</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>借款人利息付至日期；与dataasof之差即为真实逾期天数；比nextduedate更精确直接</t>
         </is>
       </c>
-      <c r="H73" s="12" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I73" s="48" t="inlineStr">
+      <c r="I74" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J73" s="48" t="inlineStr">
+      <c r="J74" s="48" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
+      <c r="K74" s="12" t="inlineStr">
         <is>
           <t>真实逾期天数计算（当前ETL未使用）</t>
         </is>
       </c>
-      <c r="L73" s="7" t="inlineStr">
+      <c r="L74" s="131" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>✅ 100%（interestpaidthroughdate，2022-09-30~2026-11-30）</t>
         </is>
       </c>
-      <c r="M73" s="59" t="inlineStr">
+      <c r="N74" s="126" t="inlineStr">
         <is>
           <t>-- 验证 interest_paid_through_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
 SELECT loanid, dataasof, interestpaidthroughdate
 FROM   newrez.portnewrezgeneral
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezgeneral)
+WHERE  dataasof = '2026-06-01'
   AND  interestpaidthroughdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N73" s="68" t="inlineStr">
+      <c r="O74" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-05-01 | 2026-05-01 | 2026-06-01 | 2025-09-01 | 2024-06-01 | 2026-06-01 | 2026-05-01 | 2026-05-01 | 2026-06-01 | 2025-10-01（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="40" customHeight="1" s="74">
-      <c r="A74" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>2.6 贷款属性与风险增强字段 — N</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>in_auction_flag</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezgeneral.inauctionflag</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>是否当前处于拍卖程序中（1=是）；填充率低但信号强——任何有值记录均表明止赎接近完成</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="inlineStr">
-        <is>
-          <t>0 / 1（有值即高优先级信号）</t>
-        </is>
-      </c>
-      <c r="I74" s="48" t="inlineStr">
-        <is>
-          <t>0 / 1</t>
-        </is>
-      </c>
-      <c r="J74" s="48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>拍卖临近高优先级处理（当前ETL未使用）</t>
-        </is>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
-        <is>
-          <t>✅ 7.7% (有值即高信号)</t>
-        </is>
-      </c>
-      <c r="M74" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 in_auction_flag 取值范围
--- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, inauctionflag, COUNT(*) AS cnt
-FROM   newrez.portnewrezgeneral
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezgeneral)
-GROUP  BY dataasof, inauctionflag ORDER BY cnt DESC;</t>
-        </is>
-      </c>
-      <c r="N74" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] 0:5045 | 1:7</t>
+      <c r="S74" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T74" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -8600,145 +9887,174 @@
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
+          <t>in_auction_flag</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezgeneral.inauctionflag</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>是否当前处于拍卖程序中（1=是）；填充率低但信号强——任何有值记录均表明止赎接近完成</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1（有值即高优先级信号）</t>
+        </is>
+      </c>
+      <c r="I75" s="48" t="inlineStr">
+        <is>
+          <t>0 / 1</t>
+        </is>
+      </c>
+      <c r="J75" s="48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>拍卖临近高优先级处理（当前ETL未使用）</t>
+        </is>
+      </c>
+      <c r="L75" s="131" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>✅ 7.7% (有值即高信号)</t>
+        </is>
+      </c>
+      <c r="N75" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 in_auction_flag 取值范围
+-- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, inauctionflag, COUNT(*) AS cnt
+FROM   newrez.portnewrezgeneral
+WHERE  dataasof = '2026-06-01'
+GROUP  BY dataasof, inauctionflag ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="O75" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] 0:5045 | 1:7</t>
+        </is>
+      </c>
+      <c r="S75" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T75" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1" s="74">
+      <c r="A76" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>2.6 贷款属性与风险增强字段 — N</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
           <t>borrower_deceased_flag</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezgeneral.borrowerdeceasedflag</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="F75" s="12" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G75" s="12" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>借款人是否已死亡（1=是）；影响止赎法律流程——需通知遗产代表；部分州需重新确认贷款归属</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>0 / 1（有值即高影响）</t>
         </is>
       </c>
-      <c r="I75" s="48" t="inlineStr">
+      <c r="I76" s="48" t="inlineStr">
         <is>
           <t>0 / 1</t>
         </is>
       </c>
-      <c r="J75" s="48" t="inlineStr">
+      <c r="J76" s="48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K75" s="12" t="inlineStr">
+      <c r="K76" s="12" t="inlineStr">
         <is>
           <t>遗产代表通知 / 合规流程调整（当前ETL未使用）</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr">
+      <c r="L76" s="131" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>✅ 5.1% (有值即高影响)</t>
         </is>
       </c>
-      <c r="M75" s="59" t="inlineStr">
+      <c r="N76" s="126" t="inlineStr">
         <is>
           <t>-- 验证 borrower_deceased_flag 取值范围
 -- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, borrowerdeceasedflag, COUNT(*) AS cnt
 FROM   newrez.portnewrezgeneral
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezgeneral)
+WHERE  dataasof = '2026-06-01'
 GROUP  BY dataasof, borrowerdeceasedflag ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N75" s="68" t="inlineStr">
+      <c r="O76" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 0:5036 | 1:16</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="40" customHeight="1" s="74">
-      <c r="A76" s="13" t="n">
-        <v>68</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>2.6 贷款属性与风险增强字段 — N</t>
-        </is>
-      </c>
-      <c r="C76" s="19" t="inlineStr">
-        <is>
-          <t>reason_for_default</t>
-        </is>
-      </c>
-      <c r="D76" s="20" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezgeneral.reasonfordefault</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>违约根本原因自由文本（如失业/收入减少/医疗支出）；LM方案选择的关键输入</t>
-        </is>
-      </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t>自由文本</t>
-        </is>
-      </c>
-      <c r="I76" s="49" t="inlineStr">
-        <is>
-          <t>自由文本（借款人违约原因）</t>
-        </is>
-      </c>
-      <c r="J76" s="49" t="inlineStr">
-        <is>
-          <t>Unable to Contact Borrower</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>LM方案选择 / 风险分类 / 投资人报告（当前ETL未使用）</t>
-        </is>
-      </c>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>✅ 46.2%（reasonfordefault：Unable to Contact Borrower | Reduction in Income | Excessive Obligations 等15+种）</t>
-        </is>
-      </c>
-      <c r="M76" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 reason_for_default 取值范围
--- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, reasonfordefault AS val, COUNT(*) AS cnt
-FROM   newrez.portnewrezgeneral
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezgeneral)
-  AND  reasonfordefault IS NOT NULL AND reasonfordefault != ''
-GROUP  BY dataasof, reasonfordefault ORDER BY cnt DESC LIMIT 30;</t>
-        </is>
-      </c>
-      <c r="N76" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] Unable to Contact Borrower:39 | Reduction in Borrower's Income:9 | Within Grace Period:8 | Other/No applicable codes:6 | Servicing Problems:3 | Excessive Obligations:3 | Death of Primary Borrower:3 | Payment Dispute:2 | Unemployment:2 | Customer Pay Period:2 | Illness of Borrower's Family Member:2 | Tenant Not Paying:1 | Overlooked:1 | Illness of Primary Borrower:1 | Inability to Rent Property:1</t>
+      <c r="S76" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T76" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
         </is>
       </c>
     </row>
@@ -8753,281 +10069,418 @@
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
+          <t>reason_for_default</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezgeneral.reasonfordefault</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>违约根本原因自由文本（如失业/收入减少/医疗支出）；LM方案选择的关键输入</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>自由文本</t>
+        </is>
+      </c>
+      <c r="I77" s="49" t="inlineStr">
+        <is>
+          <t>自由文本（借款人违约原因）</t>
+        </is>
+      </c>
+      <c r="J77" s="49" t="inlineStr">
+        <is>
+          <t>Unable to Contact Borrower</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>LM方案选择 / 风险分类 / 投资人报告（当前ETL未使用）</t>
+        </is>
+      </c>
+      <c r="L77" s="132" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>✅ 46.2%（reasonfordefault：Unable to Contact Borrower | Reduction in Income | Excessive Obligations 等15+种）</t>
+        </is>
+      </c>
+      <c r="N77" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 reason_for_default 取值范围
+-- 源表: newrez.portnewrezgeneral | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, reasonfordefault AS val, COUNT(*) AS cnt
+FROM   newrez.portnewrezgeneral
+WHERE  dataasof = '2026-06-01'
+  AND  reasonfordefault IS NOT NULL AND reasonfordefault != ''
+GROUP  BY dataasof, reasonfordefault ORDER BY cnt DESC LIMIT 30;</t>
+        </is>
+      </c>
+      <c r="O77" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] Unable to Contact Borrower:39 | Reduction in Borrower's Income:9 | Within Grace Period:8 | Other/No applicable codes:6 | Servicing Problems:3 | Excessive Obligations:3 | Death of Primary Borrower:3 | Payment Dispute:2 | Unemployment:2 | Customer Pay Period:2 | Illness of Borrower's Family Member:2 | Tenant Not Paying:1 | Overlooked:1 | Illness of Primary Borrower:1 | Inability to Rent Property:1</t>
+        </is>
+      </c>
+      <c r="S77" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T77" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1" s="74">
+      <c r="A78" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>2.6 贷款属性与风险增强字段 — N</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
           <t>hold_1_comment</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D78" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold1comment</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="F77" s="13" t="inlineStr">
+      <c r="F78" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G77" s="13" t="inlineStr">
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>Hold槽1详细备注；补充hold_1_description的具体背景（如'BK案号2026-123'/'等待LM决策'）</t>
         </is>
       </c>
-      <c r="H77" s="13" t="inlineStr">
+      <c r="H78" s="13" t="inlineStr">
         <is>
           <t>自由文本</t>
         </is>
       </c>
-      <c r="I77" s="49" t="inlineStr">
+      <c r="I78" s="49" t="inlineStr">
         <is>
           <t>自由文本</t>
         </is>
       </c>
-      <c r="J77" s="49" t="inlineStr">
+      <c r="J78" s="49" t="inlineStr">
         <is>
           <t>Awaiting Bankruptcy Resolution</t>
         </is>
       </c>
-      <c r="K77" s="13" t="inlineStr">
+      <c r="K78" s="13" t="inlineStr">
         <is>
           <t>Hold面板补充说明（当前ETL未使用）</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="L78" s="132" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
         <is>
           <t>✅ 82.1%</t>
         </is>
       </c>
-      <c r="M77" s="59" t="inlineStr">
+      <c r="N78" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_1_comment 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold1comment
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold1comment IS NOT NULL AND fchold1comment != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N77" s="68" t="inlineStr">
+      <c r="O78" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 12/01/2025 | Delinquency Review | Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 06/01/2026 | Delinquency Review | Delinquency Review | Delinquency Review | Praecipe to reinstate complaint received.  Same will be sent to the sheriff to be included with service to effectuate completion.  ETA for service completion is 3-4 weeks.  Our firm last followed up for the needed affidavits on 5/8/26.  Next update 6/5/26. | Chapter 7 filed 04/27/2026. Case 2611770. | Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 11/01/2025 | Service still being attempted for The Unknown Tenant in Possession, all others have been served as of 5/28. Next follow up 6/11 eta for completion 6/18（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="40" customHeight="1" s="74">
-      <c r="A78" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="S78" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T78" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1" s="74">
+      <c r="A79" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
         <is>
           <t>2.6 贷款属性与风险增强字段 — N</t>
         </is>
       </c>
-      <c r="C78" s="19" t="inlineStr">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>hold_2_comment</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D79" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold2comment</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="F78" s="13" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G78" s="13" t="inlineStr">
+      <c r="G79" s="13" t="inlineStr">
         <is>
           <t>Hold槽2详细备注</t>
         </is>
       </c>
-      <c r="H78" s="13" t="inlineStr">
+      <c r="H79" s="13" t="inlineStr">
         <is>
           <t>自由文本</t>
         </is>
       </c>
-      <c r="I78" s="49" t="inlineStr">
+      <c r="I79" s="49" t="inlineStr">
         <is>
           <t>自由文本</t>
         </is>
       </c>
-      <c r="J78" s="49" t="inlineStr">
+      <c r="J79" s="49" t="inlineStr">
         <is>
           <t>Awaiting Court Scheduling</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
+      <c r="K79" s="13" t="inlineStr">
         <is>
           <t>Hold面板补充说明（当前ETL未使用）</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L79" s="132" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>✅ 82.1%</t>
         </is>
       </c>
-      <c r="M78" s="59" t="inlineStr">
+      <c r="N79" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_2_comment 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold2comment
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold2comment IS NOT NULL AND fchold2comment != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N78" s="68" t="inlineStr">
+      <c r="O79" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Delinquency Review | Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 07/01/2026 | Delinquency Review | Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 06/01/2026 | Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 06/01/2026 | Funds received that could reinstate or payoff the loan:  Unapplied balance: 0.00   Due Date: 04/08/2026 | Service was initiated 3/13/26. We are currently pending the return of the affidavits of service. This process may take upwards of 45-60 days. Firm last followed up regarding same on 4/10/26.  ETA for completion is 3-4 weeks. Next update 5/8/26. | Pending signature required document to proceed with foreclosure action. | Notice of Sale sent for filing 10/24/2025. ETA for first legal filing is 10/30/2025. Follo …</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="40" customHeight="1" s="74">
-      <c r="A79" s="13" t="n">
-        <v>71</v>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
+      <c r="S79" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T79" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1" s="74">
+      <c r="A80" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>2.6 贷款属性与风险增强字段 — N</t>
         </is>
       </c>
-      <c r="C79" s="19" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>hold_3_comment</t>
         </is>
       </c>
-      <c r="D79" s="20" t="inlineStr">
+      <c r="D80" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezfc.fchold3comment</t>
         </is>
       </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="F80" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G79" s="13" t="inlineStr">
+      <c r="G80" s="13" t="inlineStr">
         <is>
           <t>Hold槽3详细备注</t>
         </is>
       </c>
-      <c r="H79" s="13" t="inlineStr">
+      <c r="H80" s="13" t="inlineStr">
         <is>
           <t>自由文本</t>
         </is>
       </c>
-      <c r="I79" s="49" t="inlineStr">
+      <c r="I80" s="49" t="inlineStr">
         <is>
           <t>自由文本</t>
         </is>
       </c>
-      <c r="J79" s="49" t="inlineStr">
+      <c r="J80" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K79" s="13" t="inlineStr">
+      <c r="K80" s="13" t="inlineStr">
         <is>
           <t>Hold面板补充说明（当前ETL未使用）</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="L80" s="132" t="inlineStr">
+        <is>
+          <t>N/A — Newrez 已提供但系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
         <is>
           <t>✅ 82.1%</t>
         </is>
       </c>
-      <c r="M79" s="59" t="inlineStr">
+      <c r="N80" s="126" t="inlineStr">
         <is>
           <t>-- 验证 hold_3_comment 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezfc | 运行于: mysql_dev
 SELECT loanid, dataasof, fchold3comment
 FROM   newrez.portnewrezfc
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezfc)
+WHERE  dataasof = '2026-06-01'
   AND  fchold3comment IS NOT NULL AND fchold3comment != ''
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N79" s="68" t="inlineStr">
+      <c r="O80" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] Our firm is pending receipt of the original note to proceed with the foreclosure, once received we will be able to prepare complaint for verification. | Delay Reason: Pending Recording, Hold Start Date: 2026-04-24, Date of Delay: 2026-04-23, Anticipated Resolution ETA: 2026-05-01 | unable to proceed until allonge is received. RID: 862116504   | Notice of Sale sent for filing on 4/27/2026. ETA for completion of NOS posted milestone is 4/30/2026. | Pending signature required document to proceed with foreclosure action. | Unable to proceed, pending Guaranty Agreement-RID: 861370088 | Pending signature required document to proceed with foreclosure action. | Pending receipt Note Allonge requested | AOM Needed from Mortgage Electronic Registration Systems, Inc., as nominee for A&amp;D Mortgage LLC, Its Successors and Assigns To: Alic Archwest Mortgage Trust, To Proceed to Fi …</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="18" customHeight="1" s="74">
-      <c r="A80" s="119" t="inlineStr">
+      <c r="S80" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — 系统尚未使用（不入 BPS 同步表）</t>
+        </is>
+      </c>
+      <c r="T80" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1" s="74">
+      <c r="A81" s="119" t="inlineStr">
         <is>
           <t>Section 3.1 — LM周期字段 — Loss Mitigation Cycle面板（来源：newrez.portnewrezlm）</t>
         </is>
       </c>
-      <c r="B80" s="70" t="n"/>
-      <c r="C80" s="70" t="n"/>
-      <c r="D80" s="70" t="n"/>
-      <c r="E80" s="70" t="n"/>
-      <c r="F80" s="70" t="n"/>
-      <c r="G80" s="70" t="n"/>
-      <c r="H80" s="70" t="n"/>
-      <c r="I80" s="70" t="n"/>
-      <c r="J80" s="71" t="n"/>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="3" t="n"/>
-    </row>
-    <row r="81" ht="40" customHeight="1" s="74">
-      <c r="A81" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B81" s="70" t="n"/>
+      <c r="C81" s="70" t="n"/>
+      <c r="D81" s="70" t="n"/>
+      <c r="E81" s="70" t="n"/>
+      <c r="F81" s="70" t="n"/>
+      <c r="G81" s="70" t="n"/>
+      <c r="H81" s="70" t="n"/>
+      <c r="I81" s="70" t="n"/>
+      <c r="J81" s="71" t="n"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="M81" s="3" t="n"/>
+    </row>
+    <row r="82" ht="40" customHeight="1" s="74">
+      <c r="A82" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>lm_deal</t>
         </is>
       </c>
-      <c r="D81" s="17" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.lmdeal</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>INT→VARCHAR</t>
         </is>
       </c>
-      <c r="F81" s="12" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G81" s="12" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>LM策略大类（整数编码）；ETL解码为文本：Evaluation/Modification/Short Sale/DIL等；反映本次还款宽松尝试的整体方向</t>
         </is>
       </c>
-      <c r="H81" s="12" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>需ETL解码：int→文本（如7→'DIL'）；必须附解码映射表</t>
         </is>
       </c>
-      <c r="I81" s="65" t="inlineStr">
+      <c r="I82" s="65" t="inlineStr">
         <is>
           <t>Evaluation
 Modification
@@ -9039,22 +10492,27 @@
 Payoff</t>
         </is>
       </c>
-      <c r="J81" s="48" t="inlineStr">
+      <c r="J82" s="48" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="K81" s="12" t="inlineStr">
+      <c r="K82" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.deal列</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="L82" s="131" t="inlineStr">
+        <is>
+          <t>整数码 lmdeal 经 portnewrezdatadic 解码为文本（如 7→DIL）→ deal</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="inlineStr">
         <is>
           <t>✅ 整数编码（lmdeal: 1=Modification | 2=Evaluation | 4=Payment Plan | 5=Forbearance | 6=Short Sale | 7=DIL | 9=Payoff | 11=Deferment；ETL解码为文本）</t>
         </is>
       </c>
-      <c r="M81" s="59" t="inlineStr">
+      <c r="N82" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_deal 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
@@ -9063,7 +10521,7 @@
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, lmdeal,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE lmdeal IS NOT NULL
+  FROM newrez.portnewrezlm WHERE lmdeal IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.lmdeal, b.deal, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -9074,52 +10532,67 @@
 GROUP  BY l.lmdeal, b.deal ORDER BY l.lmdeal, cnt DESC;</t>
         </is>
       </c>
-      <c r="N81" s="68" t="inlineStr">
+      <c r="O82" s="68" t="inlineStr">
         <is>
           <t>1 Modification:194 | 1 Evaluation:2 | 2 Evaluation:104 | 4 Payment Plan:37 | 5 Forbearance:51 | 6 Short Sale:9 | 7 DIL:10 | 9 Payoff:1 | 11 Deferment:50</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="40" customHeight="1" s="74">
-      <c r="A82" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="S82" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS deal 取值（dist）— lmdeal 解码文本
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `deal` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `deal` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T82" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Modification:207 | Evaluation:115 | ∅NULL:72 | Forbearance:57 | Deferment:56 | Payment Plan:39 | Short Sale:12 | DIL:10 | Payoff:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1" s="74">
+      <c r="A83" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C82" s="16" t="inlineStr">
+      <c r="C83" s="16" t="inlineStr">
         <is>
           <t>lm_program</t>
         </is>
       </c>
-      <c r="D82" s="17" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.lmprogram</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>INT→VARCHAR</t>
         </is>
       </c>
-      <c r="F82" s="12" t="inlineStr">
+      <c r="F83" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G83" s="12" t="inlineStr">
         <is>
           <t>具体执行方案（整数编码）；Deal大类内的子方案；直接决定合规和审批路径</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H83" s="12" t="inlineStr">
         <is>
           <t>需ETL解码：int→文本（如10→'Deed-in-Lieu'）；必须附解码映射表</t>
         </is>
       </c>
-      <c r="I82" s="65" t="inlineStr">
+      <c r="I83" s="65" t="inlineStr">
         <is>
           <t>Evaluation
 Bridger mod
@@ -9129,22 +10602,27 @@
 Repayment Plan 等20+种</t>
         </is>
       </c>
-      <c r="J82" s="48" t="inlineStr">
+      <c r="J83" s="48" t="inlineStr">
         <is>
           <t>Bridger mod</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr">
+      <c r="K83" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.program列</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr">
+      <c r="L83" s="131" t="inlineStr">
+        <is>
+          <t>整数码 lmprogram 经 portnewrezdatadic 解码为文本（如 10→Deed-in-Lieu）→ program</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>✅ 整数编码（lmprogram: 21=Evaluation | 73=Deferment | 419=Bridger mod | 396=VA Traditional 等20+种；ETL解码为文本）</t>
         </is>
       </c>
-      <c r="M82" s="59" t="inlineStr">
+      <c r="N83" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_program 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
@@ -9153,7 +10631,7 @@
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, lmprogram,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE lmprogram IS NOT NULL
+  FROM newrez.portnewrezlm WHERE lmprogram IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.lmprogram, b.program, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -9164,52 +10642,67 @@
 GROUP  BY l.lmprogram, b.program ORDER BY l.lmprogram, cnt DESC;</t>
         </is>
       </c>
-      <c r="N82" s="68" t="inlineStr">
+      <c r="O83" s="68" t="inlineStr">
         <is>
           <t>8 Short Sale:9 | 10 Deed-in-Lieu:10 | 12 Short-term Forbearance:41 | 14 Unemployment Forbearance:6 | 21 Evaluation:103 | 25 Payoff:1 | 29 Repayment Plan:37 | 73 Deferment:50 | 151 Disaster Forbearance:2 | 215 Short-term FB COVID (RETIRED 2023-11-01):2 | 240 SLS Standard Mod:26 | 273 Standard Proprietary Modification:9 | 346 FHA Recovery Mod (40yr):1 | 348 FHA Recovery SAPC:16 | 358 SLS Non-Standard Mod:1 | 364 VA 30 Year Modification:2 | 365 VA 40 Year Modification:2 | 396 VA Traditional:30 | 405 VASP No Trial:7 | 419 Bridger mod:38 | 496 Evaluation:2</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="40" customHeight="1" s="74">
-      <c r="A83" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="S83" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS program 取值（dist）— lmprogram 解码文本
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `program` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `program` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T83" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Evaluation:114 | ∅NULL:72 | Deferment:56 | 496.0:55 | Short-term Forbearance:47 | Repayment Plan:39 | Bridger mod:38 | VA Traditional:30 | SLS Standard Mod:26 | FHA Recovery SAPC:16 | 498.0:14 | Short Sale:12 | Deed-in-Lieu:10 | Standard Proprietary Modification:9 | VASP No Trial:7 | Unemployment Forbearance:6 | 499.0:4 | VA 40 Year Modification:2 | VA 30 Year Modification:2 | Disaster Forbearance:2 | Short-term FB COVID (RETIRED 2023-11-01):2 | +7 个取值各1笔(含 531.0/527.0/500.0 等未解码码):7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1" s="74">
+      <c r="A84" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>lm_status</t>
         </is>
       </c>
-      <c r="D83" s="17" t="inlineStr">
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.lmstatus</t>
         </is>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>INT→VARCHAR</t>
         </is>
       </c>
-      <c r="F83" s="12" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G83" s="12" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>当前LM周期的工作流进度状态（整数编码）</t>
         </is>
       </c>
-      <c r="H83" s="12" t="inlineStr">
+      <c r="H84" s="12" t="inlineStr">
         <is>
           <t>需ETL解码：int→文本（如112→'Awaiting MI Approval'）；必须附解码映射表</t>
         </is>
       </c>
-      <c r="I83" s="65" t="inlineStr">
+      <c r="I84" s="65" t="inlineStr">
         <is>
           <t>Workout Denial
 Pending Financials
@@ -9236,22 +10729,27 @@
 （实测22种；字典完整域约150码，完整 code→text 见数据字典/Redshift portnewrezdatadic，状态流转见 doc 18 §4.5）</t>
         </is>
       </c>
-      <c r="J83" s="48" t="inlineStr">
+      <c r="J84" s="48" t="inlineStr">
         <is>
           <t>Pending Financials</t>
         </is>
       </c>
-      <c r="K83" s="12" t="inlineStr">
+      <c r="K84" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.lmc_status列</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="L84" s="131" t="inlineStr">
+        <is>
+          <t>整数码 lmstatus 经 portnewrezdatadic 解码为文本（如 112→Workout Denial）→ lmc_status</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="inlineStr">
         <is>
           <t>✅ 整数编码（lmstatus: 166=Pending Financials | 112=Workout Denial | 5=Document Follow-up 等20+种；ETL解码为文本）</t>
         </is>
       </c>
-      <c r="M83" s="59" t="inlineStr">
+      <c r="N84" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_status 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
@@ -9260,7 +10758,7 @@
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, lmstatus,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE lmstatus IS NOT NULL
+  FROM newrez.portnewrezlm WHERE lmstatus IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.lmstatus, b.lmc_status, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -9271,204 +10769,259 @@
 GROUP  BY l.lmstatus, b.lmc_status ORDER BY l.lmstatus, cnt DESC;</t>
         </is>
       </c>
-      <c r="N83" s="68" t="inlineStr">
+      <c r="O84" s="68" t="inlineStr">
         <is>
           <t>5 Document Follow-up:72 | 13 Follow up for 1st Trial Payment:4 | 13 Pending Financials :1 | 20 Book mod:24 | 20 Follow up for 2nd Trial Payment:2 | 20 Follow up for 1st Trial Payment:1 | 20 Monitor for Mod Agreement – Final Trial Payment Due:1 | 24 Awaiting investor approval:1 | 25 Monitor for pmts/funds:9 | 25 Submitted for Approval:1 | 45 Countered by Supervisor:2 | 47 Monitor for Mod Agreement:3 | 112 Workout Denial:144 | 112 Document Follow-up:1 | 112 Awaiting MI Approval:1 | 112 Monitor for pmts/funds:1 | 112 Pending Financials :1 | 113 Monitor Forbearance:27 | 116 Not Assigned:1 | 126 DIL Title Ordered:1 | 127 Negotiate DIL liens:1 | 135 DIL Sent for Recording:1 | 139 Deferment Plan In Progress:11 | 140 Deferment Agreement Ordered:21 | 166 Pending Financials :113 | 172 Liquidation Referral:7 | 186 Follow up for 1st Trial Payment:1 | 186 Monitor for Mod Agreement – Final Trial Payme …</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="40" customHeight="1" s="74">
-      <c r="A84" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="S84" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS lmc_status 取值（dist）— lmstatus 解码文本
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `lmc_status` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `lmc_status` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T84" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Workout Denial:160 | Pending Financials :127 | Document Follow-up:74 | ∅NULL:72 | Monitor Forbearance:31 | Book mod:28 | Deferment Agreement Ordered:23 | Deferment Plan In Progress:13 | Monitor for pmts/funds:10 | Liquidation Referral:8 | Follow up for 1st Trial Payment:5 | Solicitation Offered:4 | Monitor for Mod Agreement:3 | +9 个取值≤2笔:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1" s="74">
+      <c r="A85" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>lm_cycle_open_date</t>
         </is>
       </c>
-      <c r="D84" s="17" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.dealstartdate</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F84" s="12" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G85" s="12" t="inlineStr">
         <is>
           <t>本次LM周期开始日；与lm_deal共同构成唯一标识</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H85" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I84" s="48" t="inlineStr">
+      <c r="I85" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J84" s="48" t="inlineStr">
+      <c r="J85" s="48" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="K84" s="12" t="inlineStr">
+      <c r="K85" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.cycle_opened_date</t>
         </is>
       </c>
-      <c r="L84" s="7" t="inlineStr">
+      <c r="L85" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（dealstartdate → cycle_opened_date）</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M84" s="59" t="inlineStr">
+      <c r="N85" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_cycle_open_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezlm | 运行于: mysql_dev
 SELECT loanid, dataasof, dealstartdate
 FROM   newrez.portnewrezlm
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezlm)
+WHERE  dataasof = '2026-06-01'
   AND  dealstartdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N84" s="68" t="inlineStr">
+      <c r="O85" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-09-18 | 2026-04-28 | 2026-03-06 | 2025-07-18 | 2025-05-23 | 2025-09-19 | 2025-11-05 | 2025-12-10 | 2026-02-25 | 2026-03-31（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="85" ht="40" customHeight="1" s="74">
-      <c r="A85" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="S85" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS cycle_opened_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`cycle_opened_date`) AS non_null,
+       MIN(`cycle_opened_date`) AS min_dt, MAX(`cycle_opened_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation;</t>
+        </is>
+      </c>
+      <c r="T85" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 568/569 · 区间 2020-08-17~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1" s="74">
+      <c r="A86" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>lm_cycle_close_date</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.lmremovaldate</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F85" s="12" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G85" s="12" t="inlineStr">
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>本次LM周期结束日；NULL=仍在进行中</t>
         </is>
       </c>
-      <c r="H85" s="12" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD；NULL=仍活跃</t>
         </is>
       </c>
-      <c r="I85" s="48" t="inlineStr">
+      <c r="I86" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD（空=进行中）</t>
         </is>
       </c>
-      <c r="J85" s="48" t="inlineStr">
+      <c r="J86" s="48" t="inlineStr">
         <is>
           <t>2024-03-15</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr">
+      <c r="K86" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.cycle_closed_date</t>
         </is>
       </c>
-      <c r="L85" s="7" t="inlineStr">
+      <c r="L86" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（lmremovaldate → cycle_closed_date；NULL=进行中）</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M85" s="59" t="inlineStr">
+      <c r="N86" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_cycle_close_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezlm | 运行于: mysql_dev
 SELECT loanid, dataasof, lmremovaldate
 FROM   newrez.portnewrezlm
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezlm)
+WHERE  dataasof = '2026-06-01'
   AND  lmremovaldate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N85" s="68" t="inlineStr">
+      <c r="O86" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-07 | 2026-05-03 | 2026-05-08 | 2026-05-20 | 2025-12-03 | 2026-05-07 | 2026-05-01 | 2025-09-08 | 2025-05-27 | 2025-09-29（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="40" customHeight="1" s="74">
-      <c r="A86" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="S86" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS cycle_closed_date 取值（date）— NULL=进行中
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`cycle_closed_date`) AS non_null,
+       MIN(`cycle_closed_date`) AS min_dt, MAX(`cycle_closed_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation;</t>
+        </is>
+      </c>
+      <c r="T86" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 511/569 · 区间 2020-09-22~2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1" s="74">
+      <c r="A87" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C87" s="16" t="inlineStr">
         <is>
           <t>lm_final_disposition</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.lmdecision</t>
         </is>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>INT→VARCHAR</t>
         </is>
       </c>
-      <c r="F86" s="12" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G87" s="12" t="inlineStr">
         <is>
           <t>本次LM周期最终结论；直接决定FCL走向：'Referral to FC'→FCL继续；'Approved'→FCL暂停</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H87" s="12" t="inlineStr">
         <is>
           <t>需ETL解码：int→文本；必须附解码映射表</t>
         </is>
       </c>
-      <c r="I86" s="65" t="inlineStr">
+      <c r="I87" s="65" t="inlineStr">
         <is>
           <t>Pending
 Modification Complete
@@ -9482,22 +11035,27 @@
 DIL Complete 等</t>
         </is>
       </c>
-      <c r="J86" s="48" t="inlineStr">
+      <c r="J87" s="48" t="inlineStr">
         <is>
           <t>Referral to FC</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr">
+      <c r="K87" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.final_disposition列</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="L87" s="131" t="inlineStr">
+        <is>
+          <t>整数码 lmdecision 经 portnewrezdatadic 解码为文本（如 6→Referral to FC）→ final_disposition</t>
+        </is>
+      </c>
+      <c r="M87" s="7" t="inlineStr">
         <is>
           <t>✅ 整数编码（lmdecision: 99=Pending | 6=Referral to FC | 10=Request Incomplete | 11=LMS Opened in Error 等；ETL解码）</t>
         </is>
       </c>
-      <c r="M86" s="59" t="inlineStr">
+      <c r="N87" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_final_disposition 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
@@ -9506,7 +11064,7 @@
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, lmdecision,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE lmdecision IS NOT NULL
+  FROM newrez.portnewrezlm WHERE lmdecision IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.lmdecision, b.final_disposition, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -9517,52 +11075,67 @@
 GROUP  BY l.lmdecision, b.final_disposition ORDER BY l.lmdecision, cnt DESC;</t>
         </is>
       </c>
-      <c r="N86" s="68" t="inlineStr">
+      <c r="O87" s="68" t="inlineStr">
         <is>
           <t>1 Modification Complete:15 | 1 Pending:2 | 3 DIL Complete:1 | 4 Forbearance Complete:16 | 4 Pending:2 | 5 Reinstated/Current:32 | 5 Pending:2 | 5 Request Incomplete/Failed to Provide Information:1 | 6 Referral to FC:110 | 6 Pending:4 | 7 Not Eligible for Loss Mitigation:7 | 10 Request Incomplete/Failed to Provide Information:94 | 10 Pending:4 | 11 LMS Opened in Error:52 | 14 Deferment Completed:30 | 17 Full Pay Off:7 | 18 FC Sale Held:2 | 99 Pending:77</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="40" customHeight="1" s="74">
-      <c r="A87" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="S87" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS final_disposition 取值（dist）— lmdecision 解码文本
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `final_disposition` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `final_disposition` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T87" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Referral to FC:123 | Request Incomplete/Failed to Provide Information:102 | Pending:97 | ∅NULL:72 | LMS Opened in Error:53 | Reinstated/Current:36 | Deferment Completed:33 | Forbearance Complete:19 | Modification Complete:17 | Not Eligible for Loss Mitigation:7 | Full Pay Off:7 | FC Sale Held:2 | DIL Complete:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1" s="74">
+      <c r="A88" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>lm_denial_reason</t>
         </is>
       </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.denialreason</t>
         </is>
       </c>
-      <c r="E87" s="12" t="inlineStr">
+      <c r="E88" s="12" t="inlineStr">
         <is>
           <t>INT→VARCHAR</t>
         </is>
       </c>
-      <c r="F87" s="12" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G87" s="12" t="inlineStr">
+      <c r="G88" s="12" t="inlineStr">
         <is>
           <t>LM被拒绝的具体原因（整数编码）；无拒绝时为空字符串（非NULL）</t>
         </is>
       </c>
-      <c r="H87" s="12" t="inlineStr">
+      <c r="H88" s="12" t="inlineStr">
         <is>
           <t>需ETL解码；无拒绝时提供空字符串</t>
         </is>
       </c>
-      <c r="I87" s="65" t="inlineStr">
+      <c r="I88" s="65" t="inlineStr">
         <is>
           <t>Loan not due 3+ months
 Withdrawal
@@ -9571,22 +11144,27 @@
 Failed Plan 等18种</t>
         </is>
       </c>
-      <c r="J87" s="48" t="inlineStr">
+      <c r="J88" s="48" t="inlineStr">
         <is>
           <t>Withdrawal of Request/Non-Acceptance</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr">
+      <c r="K88" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.denialreason列</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L88" s="131" t="inlineStr">
+        <is>
+          <t>整数码 denialreason 经 portnewrezdatadic 解码为文本（无拒绝为空）</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>✅ 整数编码（denialreason: 109=Loan not due 3+ months | 4=Withdrawal | 6=Ineligible 等18种；ETL解码）</t>
         </is>
       </c>
-      <c r="M87" s="59" t="inlineStr">
+      <c r="N88" s="126" t="inlineStr">
         <is>
           <t>-- 验证 lm_denial_reason 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
@@ -9595,7 +11173,7 @@
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, denialreason,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE denialreason IS NOT NULL
+  FROM newrez.portnewrezlm WHERE denialreason IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.denialreason, b.denialreason, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -9606,72 +11184,92 @@
 GROUP  BY l.denialreason, b.denialreason ORDER BY l.denialreason, cnt DESC;</t>
         </is>
       </c>
-      <c r="N87" s="68" t="inlineStr">
+      <c r="O88" s="68" t="inlineStr">
         <is>
           <t>2 Trial Plan Default:3 | 4 Withdrawal of Request/Non-Acceptance:12 | 6 Ineligible Borrower:1 | 9 Investor Not Participating:5 | 11 Default Not Imminent:1 | 20 Title Exceptions:1 | 21 Request Incomplete/Failed to Provide Documentation:22 | 30 Failed Plan:5 | 32 HDTI out of range:2 | 34 Ineligible Borrower: Not a Natural Person:1 | 50 Request Withdrawn Before Offer:1 | 53 Prev Denial – No Chg in Circumstance:1 | 59 Pre-Mod HDTI &lt; 31%:1 | 75 Declined Mod Review in favor of SS/DIL:1 | 76 HAMP Sunset:15 | 78 Buyer walked (SS):1 | 86 Request Withdrawn:2 | 95 Loan not eligible for deferment:1 | 101 Required Payment Returned / Not Received:1 | 108 Unable to achieve target payment:9 | 109 Loan not due for 3 or more monthly payments:25 | 115 Post-Mod P&amp;I Payment &gt; Current P&amp;I Payment:4 | 118 Loan not 90+ DPD :5 | 122 DTI out of range for Deferment:1 | 124 Hardship not resolved:6</t>
         </is>
       </c>
-    </row>
-    <row r="88" ht="40" customHeight="1" s="74">
-      <c r="A88" s="13" t="n">
-        <v>79</v>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="S88" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS denialreason 取值（dist）— denialreason 解码文本
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `denialreason` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `denialreason` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T88" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] (空串):351 | ∅NULL:72 | Request Incomplete/Failed to Provide Documentation:28 | Loan not due for 3 or more monthly payments:25 | HAMP Sunset:16 | Withdrawal of Request/Non-Acceptance:15 | Unable to achieve target payment:9 | Hardship not resolved:7 | Investor Not Participating:6 | Failed Plan:5 | Loan not 90+ DPD :5 | Post-Mod P&amp;I Payment &gt; Current P&amp;I Payment:4 | Trial Plan Default:4 | HDTI out of range:3 | 145.0(未解码码):1 | +18 个取值各1笔:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1" s="74">
+      <c r="A89" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>3.1 LM周期字段 — Loss M</t>
         </is>
       </c>
-      <c r="C88" s="19" t="inlineStr">
+      <c r="C89" s="19" t="inlineStr">
         <is>
           <t>borrower_intentions</t>
         </is>
       </c>
-      <c r="D88" s="20" t="inlineStr">
+      <c r="D89" s="20" t="inlineStr">
         <is>
           <t>newrez.portnewrezlm.borrowerintention</t>
         </is>
       </c>
-      <c r="E88" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>INT→VARCHAR</t>
         </is>
       </c>
-      <c r="F88" s="13" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G88" s="13" t="inlineStr">
+      <c r="G89" s="13" t="inlineStr">
         <is>
           <t>借款人声明的处置意向（整数编码）；如保留房产/短售/产权代替；CFPB Reg X相关</t>
         </is>
       </c>
-      <c r="H88" s="13" t="inlineStr">
+      <c r="H89" s="13" t="inlineStr">
         <is>
           <t>需ETL解码</t>
         </is>
       </c>
-      <c r="I88" s="49" t="inlineStr">
+      <c r="I89" s="49" t="inlineStr">
         <is>
           <t>Unknown | Retention | Disposition</t>
         </is>
       </c>
-      <c r="J88" s="49" t="inlineStr">
+      <c r="J89" s="49" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="K88" s="13" t="inlineStr">
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.borrower_intentions（CFPB Reg X）</t>
         </is>
       </c>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="L89" s="132" t="inlineStr">
+        <is>
+          <t>整数码 borrowerintention 经 portnewrezdatadic 解码为文本（Newrez 通常空）</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
         <is>
           <t>✅ 整数编码（borrowerintention: 1=Unknown | 2=Retention | 3=Disposition；SQL-D6实测）</t>
         </is>
       </c>
-      <c r="M88" s="62" t="inlineStr">
+      <c r="N89" s="120" t="inlineStr">
         <is>
           <t>-- 验证 borrower_intentions 取值范围（整数码 → BPS 解码文本）
 -- 源表: newrez.portnewrezlm JOIN bpms_dev.sync_loan_foreclosure_loss_mitigation
@@ -9680,7 +11278,7 @@
 WITH latest_lm AS (
   SELECT loanid, dealstartdate, borrowerintention,
          ROW_NUMBER() OVER (PARTITION BY loanid, dealstartdate ORDER BY dataasof DESC) AS rn
-  FROM newrez.portnewrezlm WHERE borrowerintention IS NOT NULL
+  FROM newrez.portnewrezlm WHERE borrowerintention IS NOT NULL AND dataasof &lt;= '2026-06-01'
 )
 SELECT l.borrowerintention, b.borrower_intentions, COUNT(*) AS cnt
 FROM   latest_lm l
@@ -9691,79 +11289,24 @@
 GROUP  BY l.borrowerintention, b.borrower_intentions ORDER BY l.borrowerintention, cnt DESC;</t>
         </is>
       </c>
-      <c r="N88" s="68" t="inlineStr">
+      <c r="O89" s="68" t="inlineStr">
         <is>
           <t>1 Unknown:1 | 2 Retention:47 | 3 Disposition:4</t>
         </is>
       </c>
-    </row>
-    <row r="89" ht="40" customHeight="1" s="74">
-      <c r="A89" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>3.1 LM周期字段 — Loss M</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>imminent_default</t>
-        </is>
-      </c>
-      <c r="D89" s="20" t="inlineStr">
-        <is>
-          <t>— (无对应字段)</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="F89" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr">
-        <is>
-          <t>CFPB Reg X 12 CFR 1024.41要求的即将违约标志；标记尚未逾期但面临可预见还款困难的借款人</t>
-        </is>
-      </c>
-      <c r="H89" s="13" t="inlineStr">
-        <is>
-          <t>CFPB Reg X触发条件文本</t>
-        </is>
-      </c>
-      <c r="I89" s="49" t="inlineStr">
-        <is>
-          <t>CFPB Reg X标准值</t>
-        </is>
-      </c>
-      <c r="J89" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.imminent_default（CFPB Reg X）</t>
-        </is>
-      </c>
-      <c r="L89" s="6" t="inlineStr">
-        <is>
-          <t>❌ 0% (Newrez未提供，见doc 13 Q6)</t>
-        </is>
-      </c>
-      <c r="M89" s="62" t="inlineStr">
-        <is>
-          <t>-- N/A — Newrez未提供（无可验证源）</t>
-        </is>
-      </c>
-      <c r="N89" s="68" t="inlineStr">
-        <is>
-          <t>N/A（无可验证源）</t>
+      <c r="S89" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS borrower_intentions 取值（dist）— borrowerintention 解码文本
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `borrower_intentions` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `borrower_intentions` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T89" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] (空串):442 | ∅NULL:72 | Retention:49 | Disposition:5 | Unknown:1</t>
         </is>
       </c>
     </row>
@@ -9778,158 +11321,192 @@
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
+          <t>imminent_default</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>— (无对应字段)</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>CFPB Reg X 12 CFR 1024.41要求的即将违约标志；标记尚未逾期但面临可预见还款困难的借款人</t>
+        </is>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>CFPB Reg X触发条件文本</t>
+        </is>
+      </c>
+      <c r="I90" s="49" t="inlineStr">
+        <is>
+          <t>CFPB Reg X标准值</t>
+        </is>
+      </c>
+      <c r="J90" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.imminent_default（CFPB Reg X）</t>
+        </is>
+      </c>
+      <c r="L90" s="132" t="inlineStr">
+        <is>
+          <t>N/A — 对 Newrez 恒 NULL（BPS 列存在但 Newrez 链路不填）</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>❌ 0% (Newrez未提供，见doc 13 Q6)</t>
+        </is>
+      </c>
+      <c r="N90" s="120" t="inlineStr">
+        <is>
+          <t>-- N/A — Newrez未提供（无可验证源）</t>
+        </is>
+      </c>
+      <c r="O90" s="68" t="inlineStr">
+        <is>
+          <t>N/A（无可验证源）</t>
+        </is>
+      </c>
+      <c r="S90" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS imminent_default 取值（dist）— 对 Newrez 预期恒空
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `imminent_default` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `imminent_default` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T90" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] ∅NULL:569</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1" s="74">
+      <c r="A91" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>3.1 LM周期字段 — Loss M</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
           <t>single_point_of_contact</t>
         </is>
       </c>
-      <c r="D90" s="20" t="inlineStr">
+      <c r="D91" s="20" t="inlineStr">
         <is>
           <t>— (无对应字段)</t>
         </is>
       </c>
-      <c r="E90" s="13" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="F90" s="13" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G90" s="13" t="inlineStr">
+      <c r="G91" s="13" t="inlineStr">
         <is>
           <t>CFPB Reg X 12 CFR 1024.40要求：在LM过程中贷款方必须为借款人指定唯一专属联络员</t>
         </is>
       </c>
-      <c r="H90" s="13" t="inlineStr">
+      <c r="H91" s="13" t="inlineStr">
         <is>
           <t>CFPB Reg X专属联络员姓名/ID</t>
         </is>
       </c>
-      <c r="I90" s="49" t="inlineStr">
+      <c r="I91" s="49" t="inlineStr">
         <is>
           <t>联系人姓名或工号</t>
         </is>
       </c>
-      <c r="J90" s="49" t="inlineStr">
+      <c r="J91" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="13" t="inlineStr">
+      <c r="K91" s="13" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_loss_mitigation.single_point_of_contact（CFPB Reg X）</t>
         </is>
       </c>
-      <c r="L90" s="6" t="inlineStr">
+      <c r="L91" s="132" t="inlineStr">
+        <is>
+          <t>N/A — 对 Newrez 恒 NULL（BPS 列存在但 Newrez 链路不填）</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>❌ 0% (Newrez未提供，见doc 13 Q6)</t>
         </is>
       </c>
-      <c r="M90" s="62" t="inlineStr">
+      <c r="N91" s="120" t="inlineStr">
         <is>
           <t>-- N/A — Newrez未提供（无可验证源）</t>
         </is>
       </c>
-      <c r="N90" s="68" t="inlineStr">
+      <c r="O91" s="68" t="inlineStr">
         <is>
           <t>N/A（无可验证源）</t>
         </is>
       </c>
-    </row>
-    <row r="91" ht="18" customHeight="1" s="74">
-      <c r="A91" s="119" t="inlineStr">
+      <c r="S91" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS single_point_of_contact 取值（dist）— 对 Newrez 预期恒空
+-- 表: bpms.sync_loan_foreclosure_loss_mitigation | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `single_point_of_contact` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_loss_mitigation
+GROUP  BY `single_point_of_contact` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T91" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] ∅NULL:569</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1" s="74">
+      <c r="A92" s="119" t="inlineStr">
         <is>
           <t>Section 4.1 — 破产字段 — Bankruptcy面板（来源：newrez.portnewrezbk）</t>
         </is>
       </c>
-      <c r="B91" s="70" t="n"/>
-      <c r="C91" s="70" t="n"/>
-      <c r="D91" s="70" t="n"/>
-      <c r="E91" s="70" t="n"/>
-      <c r="F91" s="70" t="n"/>
-      <c r="G91" s="70" t="n"/>
-      <c r="H91" s="70" t="n"/>
-      <c r="I91" s="70" t="n"/>
-      <c r="J91" s="71" t="n"/>
-      <c r="K91" s="2" t="n"/>
-      <c r="L91" s="3" t="n"/>
-    </row>
-    <row r="92" ht="40" customHeight="1" s="74">
-      <c r="A92" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>4.1 破产字段 — Bankrupt</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>active_bk_flag</t>
-        </is>
-      </c>
-      <c r="D92" s="17" t="inlineStr">
-        <is>
-          <t>newrez.portnewrezbk.activebkflag</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>TINYINT</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>贷款是否当前处于活跃破产保护（自动中止令）下；FCL在自动中止令期间必须依法暂停</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="inlineStr">
-        <is>
-          <t>0 / 1</t>
-        </is>
-      </c>
-      <c r="I92" s="48" t="inlineStr">
-        <is>
-          <t>0 / 1</t>
-        </is>
-      </c>
-      <c r="J92" s="48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K92" s="12" t="inlineStr">
-        <is>
-          <t>bpms_dev.sync_loan_foreclosure.variance_active_bankruptcy</t>
-        </is>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>✅ 已提供</t>
-        </is>
-      </c>
-      <c r="M92" s="59" t="inlineStr">
-        <is>
-          <t>-- 验证 active_bk_flag 取值范围
--- 源表: newrez.portnewrezbk | 运行于: mysql_dev
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
-SELECT dataasof AS data_date, activebkflag, COUNT(*) AS cnt
-FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
-GROUP  BY dataasof, activebkflag ORDER BY cnt DESC;</t>
-        </is>
-      </c>
-      <c r="N92" s="68" t="inlineStr">
-        <is>
-          <t>[data_date 2026-06-01] 0:5039 | 1:13</t>
-        </is>
-      </c>
+      <c r="B92" s="70" t="n"/>
+      <c r="C92" s="70" t="n"/>
+      <c r="D92" s="70" t="n"/>
+      <c r="E92" s="70" t="n"/>
+      <c r="F92" s="70" t="n"/>
+      <c r="G92" s="70" t="n"/>
+      <c r="H92" s="70" t="n"/>
+      <c r="I92" s="70" t="n"/>
+      <c r="J92" s="71" t="n"/>
+      <c r="K92" s="2" t="n"/>
+      <c r="M92" s="3" t="n"/>
     </row>
     <row r="93" ht="40" customHeight="1" s="74">
       <c r="A93" s="12" t="n">
@@ -9942,35 +11519,126 @@
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
+          <t>active_bk_flag</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>newrez.portnewrezbk.activebkflag</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>TINYINT</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>贷款是否当前处于活跃破产保护（自动中止令）下；FCL在自动中止令期间必须依法暂停</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1</t>
+        </is>
+      </c>
+      <c r="I93" s="48" t="inlineStr">
+        <is>
+          <t>0 / 1</t>
+        </is>
+      </c>
+      <c r="J93" s="48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>bpms_dev.sync_loan_foreclosure.variance_active_bankruptcy</t>
+        </is>
+      </c>
+      <c r="L93" s="131" t="inlineStr">
+        <is>
+          <t>N/A — BK 表无 active flag；破产存在性 = 有行</t>
+        </is>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>✅ 已提供</t>
+        </is>
+      </c>
+      <c r="N93" s="126" t="inlineStr">
+        <is>
+          <t>-- 验证 active_bk_flag 取值范围
+-- 源表: newrez.portnewrezbk | 运行于: mysql_dev
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
+SELECT dataasof AS data_date, activebkflag, COUNT(*) AS cnt
+FROM   newrez.portnewrezbk
+WHERE  dataasof = '2026-06-01'
+GROUP  BY dataasof, activebkflag ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="O93" s="68" t="inlineStr">
+        <is>
+          <t>[data_date 2026-06-01] 0:5039 | 1:13</t>
+        </is>
+      </c>
+      <c r="S93" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BK 表无 active flag；存在性=有行</t>
+        </is>
+      </c>
+      <c r="T93" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1" s="74">
+      <c r="A94" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>4.1 破产字段 — Bankrupt</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
           <t>bk_status</t>
         </is>
       </c>
-      <c r="D93" s="17" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkstatus</t>
         </is>
       </c>
-      <c r="E93" s="12" t="inlineStr">
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t>INT/VARCHAR</t>
         </is>
       </c>
-      <c r="F93" s="12" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G93" s="12" t="inlineStr">
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>当前破产案件状态（整数编码）；解码行为待确认</t>
         </is>
       </c>
-      <c r="H93" s="12" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>整数代码（解码映射待确认，见doc 13 Q7）</t>
         </is>
       </c>
-      <c r="I93" s="65" t="inlineStr">
+      <c r="I94" s="65" t="inlineStr">
         <is>
           <t>BPS 解码文本：
 Active
@@ -9980,80 +11648,100 @@
 ReliefGranted（Newrez 原始 bkstatus 1~5）</t>
         </is>
       </c>
-      <c r="J93" s="48" t="inlineStr">
+      <c r="J94" s="48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K93" s="12" t="inlineStr">
+      <c r="K94" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.bankruptcy_status</t>
         </is>
       </c>
-      <c r="L93" s="8" t="inlineStr">
+      <c r="L94" s="131" t="inlineStr">
+        <is>
+          <t>COALESCE(portnewrezdatadic[BKStatus] 解码文本, bkstatus 原始码)（Active/Discharged/Dismissed/Closed/ReliefGranted）</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="inlineStr">
         <is>
           <t>✅ 已确认：BPS 解码为文本（1→Active | 2→Discharged | 3→Dismissed | 4→Closed | 5→ReliefGranted，DB 实测）</t>
         </is>
       </c>
-      <c r="M93" s="61" t="inlineStr">
+      <c r="N94" s="128" t="inlineStr">
         <is>
           <t>-- 验证 bk_status 取值范围
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 -- BK 整数编码（Newrez 原始码；BPS 端解码情况见 col12/数据字典）
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, bkstatus AS code, COUNT(*) AS cnt
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkstatus IS NOT NULL AND bkstatus != ''
 GROUP  BY dataasof, bkstatus ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N93" s="68" t="inlineStr">
+      <c r="O94" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2:14 | 1:13 | 3:3 | 5:2 | 4:1</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="40" customHeight="1" s="74">
-      <c r="A94" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="S94" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS bankruptcy_status 取值（dist）— bkstatus 经 datadic 解码文本
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `bankruptcy_status` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_bankruptcy
+GROUP  BY `bankruptcy_status` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T94" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] Completed/Cancelled:32 | Active:16 | Discharged:15 | Dismissed:3 | ReliefGranted:2 | Closed:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1" s="74">
+      <c r="A95" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
+      <c r="C95" s="16" t="inlineStr">
         <is>
           <t>bk_legal_status</t>
         </is>
       </c>
-      <c r="D94" s="17" t="inlineStr">
+      <c r="D95" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkstage</t>
         </is>
       </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>INT/VARCHAR</t>
         </is>
       </c>
-      <c r="F94" s="12" t="inlineStr">
+      <c r="F95" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G95" s="12" t="inlineStr">
         <is>
           <t>破产法律程序阶段（整数编码）；与bk_status不同维度的分类</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H95" s="12" t="inlineStr">
         <is>
           <t>整数代码（解码映射待确认）</t>
         </is>
       </c>
-      <c r="I94" s="65" t="inlineStr">
+      <c r="I95" s="65" t="inlineStr">
         <is>
           <t>BPS 文本：
 FCBU
@@ -10069,664 +11757,834 @@
 REO（取自 portnewrezgeneral.legalstatus）</t>
         </is>
       </c>
-      <c r="J94" s="48" t="inlineStr">
+      <c r="J95" s="48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr">
+      <c r="K95" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.legal_status</t>
         </is>
       </c>
-      <c r="L94" s="8" t="inlineStr">
+      <c r="L95" s="131" t="inlineStr">
+        <is>
+          <t>直接取文本（portnewrezgeneral.legalstatus → legal_status，如 FCBU/BK13/BK7）</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="inlineStr">
         <is>
           <t>✅ 已确认：BPS legal_status 取自 portnewrezgeneral.legalstatus 文本（非 bkstage 数字码解码，DB 实测）</t>
         </is>
       </c>
-      <c r="M94" s="61" t="inlineStr">
+      <c r="N95" s="128" t="inlineStr">
         <is>
           <t>-- 验证 bk_legal_status 取值范围
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 -- BK 整数编码（Newrez 原始码；BPS 端解码情况见 col12/数据字典）
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, bkstage AS code, COUNT(*) AS cnt
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkstage IS NOT NULL AND bkstage != ''
 GROUP  BY dataasof, bkstage ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N94" s="68" t="inlineStr">
+      <c r="O95" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 8:14 | 4:5 | 10:3 | 21:2 | 7:2 | 17:1</t>
         </is>
       </c>
-    </row>
-    <row r="95" ht="40" customHeight="1" s="74">
-      <c r="A95" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="S95" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS legal_status 取值（dist）— 取自 portnewrezgeneral.legalstatus
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `legal_status` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_bankruptcy
+GROUP  BY `legal_status` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T95" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] ∅NULL:35 | BK13:12 | BK11DCH:3 | BK11:3 | FCBU:3 | BK7:3 | BK7DCH:2 | (空串):2 | REO:2 | BKD13LM:1 | BKD7LM:1 | BK13DCH:1 | FCSold:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1" s="74">
+      <c r="A96" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C96" s="16" t="inlineStr">
         <is>
           <t>bk_status_date</t>
         </is>
       </c>
-      <c r="D95" s="17" t="inlineStr">
+      <c r="D96" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkrcurrentstatusdate</t>
         </is>
       </c>
-      <c r="E95" s="12" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F95" s="12" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G95" s="12" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>当前破产状态的生效日期</t>
         </is>
       </c>
-      <c r="H95" s="12" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I95" s="48" t="inlineStr">
+      <c r="I96" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J95" s="48" t="inlineStr">
+      <c r="J96" s="48" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="K95" s="12" t="inlineStr">
+      <c r="K96" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.status_date</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="L96" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（bkfileddate → status_date；代码核实=破产申请日，非 bkrcurrentstatusdate）</t>
+        </is>
+      </c>
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M95" s="59" t="inlineStr">
+      <c r="N96" s="126" t="inlineStr">
         <is>
           <t>-- 验证 bk_status_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 SELECT loanid, dataasof, bkrcurrentstatusdate
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkrcurrentstatusdate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N95" s="68" t="inlineStr">
+      <c r="O96" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-27 | 2026-04-15 | 2025-07-12 | 2023-10-24 | 2026-04-01 | 2026-04-08 | 2026-05-26 | 2026-03-27 | 2023-11-20 | 2024-02-01（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="96" ht="40" customHeight="1" s="74">
-      <c r="A96" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="S96" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS status_date 取值（date）— 实际=bkfileddate（代码核实）
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`status_date`) AS non_null,
+       MIN(`status_date`) AS min_dt, MAX(`status_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_bankruptcy;</t>
+        </is>
+      </c>
+      <c r="T96" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 67/69 · 区间 2003-11-14~2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1" s="74">
+      <c r="A97" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C96" s="16" t="inlineStr">
+      <c r="C97" s="16" t="inlineStr">
         <is>
           <t>bk_chapter</t>
         </is>
       </c>
-      <c r="D96" s="17" t="inlineStr">
+      <c r="D97" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkchapter</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>VARCHAR/INT</t>
         </is>
       </c>
-      <c r="F96" s="12" t="inlineStr">
+      <c r="F97" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>申请的破产章节；Chapter 7（清算）/ Chapter 13（还款计划）/ Chapter 11（重组）；影响FCL恢复策略</t>
         </is>
       </c>
-      <c r="H96" s="12" t="inlineStr">
+      <c r="H97" s="12" t="inlineStr">
         <is>
           <t>7 / 11 / 13 等</t>
         </is>
       </c>
-      <c r="I96" s="48" t="inlineStr">
+      <c r="I97" s="48" t="inlineStr">
         <is>
           <t>7（清算）/ 11（重组）/ 13（个人还款计划）</t>
         </is>
       </c>
-      <c r="J96" s="48" t="inlineStr">
+      <c r="J97" s="48" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K96" s="12" t="inlineStr">
+      <c r="K97" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.chapter</t>
         </is>
       </c>
-      <c r="L96" s="7" t="inlineStr">
+      <c r="L97" s="131" t="inlineStr">
+        <is>
+          <t>CAST 为 DECIMAL（7/11/13 → chapter）</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M96" s="59" t="inlineStr">
+      <c r="N97" s="126" t="inlineStr">
         <is>
           <t>-- 验证 bk_chapter 取值范围
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 -- BK 整数编码（Newrez 原始码；BPS 端解码情况见 col12/数据字典）
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, bkchapter AS code, COUNT(*) AS cnt
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkchapter IS NOT NULL AND bkchapter != ''
 GROUP  BY dataasof, bkchapter ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N96" s="68" t="inlineStr">
+      <c r="O97" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 13:15 | 7:12 | 11:6</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="40" customHeight="1" s="74">
-      <c r="A97" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="S97" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS chapter 取值（dist）— 7/11/13
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, `chapter` AS val, COUNT(*) AS cnt
+FROM   bpms.sync_loan_foreclosure_bankruptcy
+GROUP  BY `chapter` ORDER BY cnt DESC;</t>
+        </is>
+      </c>
+      <c r="T97" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 13:38 | 7:25 | 11:6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1" s="74">
+      <c r="A98" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C98" s="16" t="inlineStr">
         <is>
           <t>bk_filed_date</t>
         </is>
       </c>
-      <c r="D97" s="17" t="inlineStr">
+      <c r="D98" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkfileddate</t>
         </is>
       </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G97" s="12" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>破产申请向法院提交的日期；BPS去重键（loanid + bkfileddate唯一标识一次破产申请）</t>
         </is>
       </c>
-      <c r="H97" s="12" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I97" s="48" t="inlineStr">
+      <c r="I98" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J97" s="48" t="inlineStr">
+      <c r="J98" s="48" t="inlineStr">
         <is>
           <t>2023-01-15</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr">
+      <c r="K98" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy（BPS去重键）</t>
         </is>
       </c>
-      <c r="L97" s="7" t="inlineStr">
+      <c r="L98" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（bkfileddate → status_date；同 bk_status_date）</t>
+        </is>
+      </c>
+      <c r="M98" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M97" s="59" t="inlineStr">
+      <c r="N98" s="126" t="inlineStr">
         <is>
           <t>-- 验证 bk_filed_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 SELECT loanid, dataasof, bkfileddate
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkfileddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N97" s="68" t="inlineStr">
+      <c r="O98" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-04-27 | 2025-12-29 | 2025-04-02 | 2025-05-27 | 2022-08-18 | 2021-03-07 | 2018-08-29 | 2025-07-12 | 2023-10-24 | 2026-04-01（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="98" ht="40" customHeight="1" s="74">
-      <c r="A98" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="S98" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS status_date 取值（date）— BPS status_date 即 bkfileddate
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`status_date`) AS non_null,
+       MIN(`status_date`) AS min_dt, MAX(`status_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_bankruptcy;</t>
+        </is>
+      </c>
+      <c r="T98" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 67/69 · 区间 2003-11-14~2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1" s="74">
+      <c r="A99" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="C99" s="16" t="inlineStr">
         <is>
           <t>bk_removal_date</t>
         </is>
       </c>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="D99" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkremovaldate</t>
         </is>
       </c>
-      <c r="E98" s="12" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F98" s="12" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G98" s="12" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>破产程序终止日期；variance_completed_bankruptcy逻辑：activebkflag=0 AND bkremovaldate IS NOT NULL</t>
         </is>
       </c>
-      <c r="H98" s="12" t="inlineStr">
+      <c r="H99" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I98" s="48" t="inlineStr">
+      <c r="I99" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J98" s="48" t="inlineStr">
+      <c r="J99" s="48" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr">
+      <c r="K99" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure.variance_completed_bankruptcy计算</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L99" s="131" t="inlineStr">
+        <is>
+          <t>N/A — BPS bankruptcy 表无 removal 列</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M98" s="59" t="inlineStr">
+      <c r="N99" s="126" t="inlineStr">
         <is>
           <t>-- 验证 bk_removal_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 SELECT loanid, dataasof, bkremovaldate
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkremovaldate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N98" s="68" t="inlineStr">
+      <c r="O99" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-12-08 | 2026-01-08 | 2023-04-20 | 2021-06-08 | 2022-12-30 | 2023-06-21 | 2026-03-25 | 2025-07-29 | 2024-06-24 | 2026-04-14（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="99" ht="40" customHeight="1" s="74">
-      <c r="A99" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="S99" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS bankruptcy 表无 removal 列</t>
+        </is>
+      </c>
+      <c r="T99" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1" s="74">
+      <c r="A100" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C100" s="16" t="inlineStr">
         <is>
           <t>mfr_filed_date</t>
         </is>
       </c>
-      <c r="D99" s="17" t="inlineStr">
+      <c r="D100" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.mfrfileddate</t>
         </is>
       </c>
-      <c r="E99" s="12" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F99" s="12" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G99" s="12" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>贷款方向破产法院提交解除自动中止令动议（MFR）的日期；MFR获批后可恢复止赎</t>
         </is>
       </c>
-      <c r="H99" s="12" t="inlineStr">
+      <c r="H100" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I99" s="48" t="inlineStr">
+      <c r="I100" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J99" s="48" t="inlineStr">
+      <c r="J100" s="48" t="inlineStr">
         <is>
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="K99" s="12" t="inlineStr">
+      <c r="K100" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.mfr_filed_date</t>
         </is>
       </c>
-      <c r="L99" s="7" t="inlineStr">
+      <c r="L100" s="131" t="inlineStr">
+        <is>
+          <t>BPS mfr_filed_date 列存在但 Newrez 提取链路硬编码 NULL（非取自 mfrfileddate）</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M99" s="59" t="inlineStr">
+      <c r="N100" s="126" t="inlineStr">
         <is>
           <t>-- 验证 mfr_filed_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 SELECT loanid, dataasof, mfrfileddate
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  mfrfileddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N99" s="68" t="inlineStr">
+      <c r="O100" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-11-04 | 2025-11-21 | 2026-04-29 | 2026-02-04 | 2025-06-10（5笔）</t>
         </is>
       </c>
-    </row>
-    <row r="100" ht="40" customHeight="1" s="74">
-      <c r="A100" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="S100" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS mfr_filed_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`mfr_filed_date`) AS non_null,
+       MIN(`mfr_filed_date`) AS min_dt, MAX(`mfr_filed_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_bankruptcy;</t>
+        </is>
+      </c>
+      <c r="T100" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 4/69 · 区间 2020-10-19~2026-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1" s="74">
+      <c r="A101" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="C101" s="16" t="inlineStr">
         <is>
           <t>mfr_hearing_results</t>
         </is>
       </c>
-      <c r="D100" s="17" t="inlineStr">
+      <c r="D101" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.mfrhearingresults</t>
         </is>
       </c>
-      <c r="E100" s="12" t="inlineStr">
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="F100" s="12" t="inlineStr">
+      <c r="F101" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G100" s="12" t="inlineStr">
+      <c r="G101" s="12" t="inlineStr">
         <is>
           <t>MFR听证会结果（整数编码，解码待确认）；获批则可恢复止赎</t>
         </is>
       </c>
-      <c r="H100" s="12" t="inlineStr">
+      <c r="H101" s="12" t="inlineStr">
         <is>
           <t>整数代码（解码映射待确认）</t>
         </is>
       </c>
-      <c r="I100" s="48" t="inlineStr">
+      <c r="I101" s="48" t="inlineStr">
         <is>
           <t>数值编码（Newrez内部）</t>
         </is>
       </c>
-      <c r="J100" s="48" t="inlineStr">
+      <c r="J101" s="48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K100" s="12" t="inlineStr">
+      <c r="K101" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.mfr_status</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr">
+      <c r="L101" s="131" t="inlineStr">
+        <is>
+          <t>N/A — BPS mfr_status 硬编码 NULL（非取自 mfrhearingresults）</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr">
         <is>
           <t>⚠️ Newrez 原始数字码（0/3/4/5/6 实测）；BPS mfr_status 列 dev 实测全空（0/64），下游填充/解码待确认</t>
         </is>
       </c>
-      <c r="M100" s="61" t="inlineStr">
+      <c r="N101" s="128" t="inlineStr">
         <is>
           <t>-- 验证 mfr_hearing_results 取值范围
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 -- BK 整数编码（Newrez 原始码；BPS 端解码情况见 col12/数据字典）
--- 快照表：已按最新 dataasof 过滤（计数=最新快照真实贷款分布，非全历史快照行数）
+-- 快照表：已固定 dataasof='2026-06-01' 过滤（与 BPS 数据日对齐，复跑结果不变；计数=该日真实贷款分布，非全历史快照行数）
 SELECT dataasof AS data_date, mfrhearingresults AS code, COUNT(*) AS cnt
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  mfrhearingresults IS NOT NULL AND mfrhearingresults != ''
 GROUP  BY dataasof, mfrhearingresults ORDER BY cnt DESC;</t>
         </is>
       </c>
-      <c r="N100" s="68" t="inlineStr">
+      <c r="O101" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 3:3 | 4:1 | 5:1</t>
         </is>
       </c>
-    </row>
-    <row r="101" ht="40" customHeight="1" s="74">
-      <c r="A101" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="S101" s="124" t="inlineStr">
+        <is>
+          <t>-- N/A — BPS mfr_status 硬编码 NULL，非来自 mfrhearingresults</t>
+        </is>
+      </c>
+      <c r="T101" s="124" t="inlineStr">
+        <is>
+          <t>N/A — 不映射到 BPS FCL 同步表（见左侧说明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1" s="74">
+      <c r="A102" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C102" s="16" t="inlineStr">
         <is>
           <t>proof_of_claim_date</t>
         </is>
       </c>
-      <c r="D101" s="17" t="inlineStr">
+      <c r="D102" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.pocfileddate</t>
         </is>
       </c>
-      <c r="E101" s="12" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F101" s="12" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G101" s="12" t="inlineStr">
+      <c r="G102" s="12" t="inlineStr">
         <is>
           <t>贷款方在破产法庭正式登记债权金额（Proof of Claim）的日期；破产合规必要步骤</t>
         </is>
       </c>
-      <c r="H101" s="12" t="inlineStr">
+      <c r="H102" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I101" s="48" t="inlineStr">
+      <c r="I102" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J101" s="48" t="inlineStr">
+      <c r="J102" s="48" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr">
+      <c r="K102" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.proof_of_claim_date</t>
         </is>
       </c>
-      <c r="L101" s="7" t="inlineStr">
+      <c r="L102" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（pocfileddate → proof_of_claim_date）</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M101" s="59" t="inlineStr">
+      <c r="N102" s="126" t="inlineStr">
         <is>
           <t>-- 验证 proof_of_claim_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 SELECT loanid, dataasof, pocfileddate
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  pocfileddate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N101" s="68" t="inlineStr">
+      <c r="O102" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2025-08-05 | 2022-10-17 | 2025-09-22 | 2023-11-15 | 2023-09-30 | 2025-06-27 | 2001-01-01 | 2010-06-17 | 2010-06-17 | 2024-03-29（10笔）</t>
         </is>
       </c>
-    </row>
-    <row r="102" ht="40" customHeight="1" s="74">
-      <c r="A102" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="S102" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS proof_of_claim_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`proof_of_claim_date`) AS non_null,
+       MIN(`proof_of_claim_date`) AS min_dt, MAX(`proof_of_claim_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_bankruptcy;</t>
+        </is>
+      </c>
+      <c r="T102" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 24/69 · 区间 2001-01-01~2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>4.1 破产字段 — Bankrupt</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="C103" s="16" t="inlineStr">
         <is>
           <t>post_petition_due_date</t>
         </is>
       </c>
-      <c r="D102" s="17" t="inlineStr">
+      <c r="D103" s="17" t="inlineStr">
         <is>
           <t>newrez.portnewrezbk.bkpostpetitionduedate</t>
         </is>
       </c>
-      <c r="E102" s="12" t="inlineStr">
+      <c r="E103" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F102" s="12" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G102" s="12" t="inlineStr">
+      <c r="G103" s="12" t="inlineStr">
         <is>
           <t>破产申请后的每月贷款付款到期日；追踪借款人在自动中止令期间是否持续还款</t>
         </is>
       </c>
-      <c r="H102" s="12" t="inlineStr">
+      <c r="H103" s="12" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I102" s="48" t="inlineStr">
+      <c r="I103" s="48" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J102" s="48" t="inlineStr">
+      <c r="J103" s="48" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="K102" s="12" t="inlineStr">
+      <c r="K103" s="12" t="inlineStr">
         <is>
           <t>bpms_dev.sync_loan_foreclosure_bankruptcy.post_petition_due_date</t>
         </is>
       </c>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="L103" s="131" t="inlineStr">
+        <is>
+          <t>直接取值（bkpostpetitionduedate → post_petition_due_date）</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
         <is>
           <t>✅ 已提供</t>
         </is>
       </c>
-      <c r="M102" s="59" t="inlineStr">
+      <c r="N103" s="126" t="inlineStr">
         <is>
           <t>-- 验证 post_petition_due_date 取值样例（最新快照取10笔，快速查看字段的样子）
 -- 源表: newrez.portnewrezbk | 运行于: mysql_dev
 SELECT loanid, dataasof, bkpostpetitionduedate
 FROM   newrez.portnewrezbk
-WHERE  dataasof = (SELECT MAX(dataasof) FROM newrez.portnewrezbk)
+WHERE  dataasof = '2026-06-01'
   AND  bkpostpetitionduedate IS NOT NULL
 LIMIT  10;</t>
         </is>
       </c>
-      <c r="N102" s="68" t="inlineStr">
+      <c r="O103" s="68" t="inlineStr">
         <is>
           <t>[data_date 2026-06-01] 2026-02-01 | 2025-11-01 | 2025-02-01 | 2021-04-01 | 2018-09-01 | 2025-09-01 | 2025-12-01 | 2026-05-01 | 2023-04-01 | 2026-04-01（10笔）</t>
+        </is>
+      </c>
+      <c r="S103" s="124" t="inlineStr">
+        <is>
+          <t>-- 验证 BPS post_petition_due_date 取值（date）
+-- 表: bpms.sync_loan_foreclosure_bankruptcy | 运行于: mysql_prod（只读）
+-- as-of: 业务快照 fctrdt≤2026-06-01（与 Newrez 源同日）；ETL 载入≈2026-06-03
+SELECT '2026-06-01' AS data_date, COUNT(*) AS total, COUNT(`post_petition_due_date`) AS non_null,
+       MIN(`post_petition_due_date`) AS min_dt, MAX(`post_petition_due_date`) AS max_dt
+FROM   bpms.sync_loan_foreclosure_bankruptcy;</t>
+        </is>
+      </c>
+      <c r="T103" s="124" t="inlineStr">
+        <is>
+          <t>[BPS prod·数据日 fctrdt≤2026-06-01·ETL载入 2026-06-03] 非空 25/69 · 区间 2018-09-01~2026-07-01</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <mergeCells count="9">
-    <mergeCell ref="A80:J80"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A92:J92"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A81:J81"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/docs/14_servicer_fcl_field_spec.xlsx
+++ b/docs/14_servicer_fcl_field_spec.xlsx
@@ -2663,13 +2663,13 @@
   <mergeCells count="10">
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>FCL Summary &gt; summary_current_step（备用，currentmilestone为空时使用）</t>
+          <t>FCL Summary &gt; summary_current_step（唯一来源，直传）；另经阶段瀑布判定 → sync_fcl_stage_info.stage</t>
         </is>
       </c>
       <c r="L24" s="131" t="inlineStr">
         <is>
-          <t>阶段瀑布判定（按里程碑优先级），存于 sync_fcl_stage_info.stage</t>
+          <t>① → summary_current_step：直传 fcstage（basic_data_pool_config.py:282；currentmilestone 不参与）；② → sync_fcl_stage_info.stage：阶段瀑布判定（按里程碑优先级：REFERRAL/SALE/SERVICE/FIRST_LEGAL/JUDGEMENT/DEMAND）</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>FCL Summary &gt; summary_current_step（最高优先级）</t>
+          <t>（原以为喂 summary_current_step；实测 ETL 不使用——见规则）</t>
         </is>
       </c>
       <c r="L25" s="131" t="inlineStr">
         <is>
-          <t>currentmilestone 非空则取之，否则取 fcstage（→ summary_current_step）</t>
+          <t>⛔ ETL 不读取 currentmilestone：summary_current_step = fcstage 直传（basic_data_pool_config.py:282；currentmilestone 全 PrefectFlow 仓库 0 引用，prod 实测 summary_current_step 值均为 fcstage 自由文本）。保留为标准接口候选，当前管道未用（更正 2026-06-10，见 doc 13 §8 Q13）</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>⚠️ 62.7% (低于可接受水平，建议提升至90%+)</t>
+          <t>⚠️ 62.7%（原始列存在但 ETL 未消费——提升填充率不影响 summary_current_step）</t>
         </is>
       </c>
       <c r="N25" s="128" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>newrez.portnewrezfc.fcjudgmententered</t>
+          <t>newrez.portnewrezfc.fcjudgmenthearingscheduled</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>直接映射；仅Judicial州（ETL代码：fcjudgment_hearing_scheduled AS timeline_judgement_date）</t>
+          <t>直接映射；仅Judicial州。ETL代码 basic_data_pool_config.py:265 `fc.fcjudgment_hearing_scheduled AS timeline_judgement_date`（源为听证排定日 fcjudgmenthearingscheduled，非 fcjudgmententered；后者→fcjudgment_end_date，不喂此字段，更正 2026-06-10）</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -17150,13 +17150,12 @@
       </c>
       <c r="E92" s="25" t="inlineStr">
         <is>
-          <t>newrez.portnewrezfc.currentmilestone / newrez.portnewrezfc.fcstage</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>currentmilestone非空→优先使用；否则回落至fcstage</t>
-        </is>
+          <t>newrez.portnewrezfc.fcstage</t>
+        </is>
+      </c>
+      <c r="F92" s="5">
+        <f> fcstage 直传（basic_data_pool_config.py:282）；currentmilestone ETL 不使用（全仓 0 引用，更正 2026-06-10）</f>
+        <v/>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
